--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X46"/>
+  <dimension ref="A1:X56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,20 +682,20 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U3" t="n">
         <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
@@ -899,25 +899,25 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-25</t>
+          <t>2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
@@ -983,27 +983,15 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOGOTA </t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CADIZ</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Entregas</t>
-        </is>
-      </c>
+          <t>C DEL PARQUE TAYRONA APTOS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -1013,14 +1001,18 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-02-21, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2026-02-13, 2026-02-21, 2026-02-27</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
@@ -1029,12 +1021,8 @@
       <c r="V8" t="n">
         <v>0</v>
       </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1044,98 +1032,50 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CHAMONIX CIUDAD LA SALLE</t>
+          <t>CADIZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Licette Tatiana Koop Santa</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-10</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-19</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1146,7 +1086,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EL CAMPO</t>
+          <t>CHAMONIX CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1157,50 +1097,48 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Juan Sebastian Ardila Castañeda</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
+          <t>Licette Tatiana Koop Santa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>TRES QUEBRADAS</t>
+          <t>CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>LUNES</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1211,42 +1149,46 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
+          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10</t>
+        </is>
+      </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EL CASTELL IBERIA RESERVADO</t>
+          <t>CIUDAD DEL PARQUE TAYRONA APTOS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1257,40 +1199,32 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Germán Baquero</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doriam Mayreth Sanchez Saenz</t>
+          <t>Carlos Sandoval</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>CIUDAD DEL PARQUE</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+          <t xml:space="preserve">JUEVES </t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LUNES</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
@@ -1298,7 +1232,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1307,95 +1241,111 @@
       <c r="P11" t="n">
         <v>4</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-17</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GALLET CIUDAD LA SALLE</t>
+          <t>DIMARO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>José Luis Suarez</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Julio Curvelo </t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1406,7 +1356,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IZOLA ZENTRAL-CITIZZEN</t>
+          <t>EL CAMPO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1417,35 +1367,45 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maicol David Sanchez Ortiz</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Juan Sebastian Ardila Castañeda</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ZENTRAL</t>
+          <t>TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1461,35 +1421,35 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-12, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="X13" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="14">
@@ -1500,7 +1460,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA ALMERIA ALSACIA RESERVADO</t>
+          <t>EL CASTELL IBERIA RESERVADO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1511,18 +1471,18 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nidia Esperanza Herrera Padilla</t>
+          <t>Doriam Mayreth Sanchez Saenz</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ALSACIA RESERVADO</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1530,13 +1490,21 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
@@ -1544,7 +1512,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1555,35 +1523,35 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-16, 2026-02-17</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="15">
@@ -1594,148 +1562,144 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA CABRERA</t>
+          <t>GALLET CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Martin Rafael Bohorquez Marrugo</t>
-        </is>
-      </c>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>TRES QUEBRADAS</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026-02-26, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA CRUZ</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>José Luis Suarez</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Erich Camargo</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="17">
@@ -1746,58 +1710,90 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LA PALMA</t>
+          <t>IZOLA ZENTRAL-CITIZZEN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Maicol David Sanchez Ortiz</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ZENTRAL</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="18">
@@ -1808,7 +1804,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LA PEÑA</t>
+          <t>LA ALMERIA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1819,45 +1815,35 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jose Alejandro Barcenas Moreno</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
+          <t>Nidia Esperanza Herrera Padilla</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>TRES QUEBRADAS</t>
+          <t>ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1873,35 +1859,35 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="U18" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" t="n">
         <v>1</v>
       </c>
-      <c r="V18" t="n">
-        <v>4</v>
-      </c>
       <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
         <v>0.25</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1912,7 +1898,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LA SCALA</t>
+          <t>LA CABRERA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1928,43 +1914,39 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Javier Manuel Gonzalez Angulo</t>
+          <t>Martin Rafael Bohorquez Marrugo</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>LA SCALA</t>
+          <t>TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -1975,35 +1957,35 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-06, 2026-02-28</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-26, 2026-02-28</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-27</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
@@ -2014,90 +1996,50 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LA TERRA ALSACIA RESERVADO</t>
+          <t>LA CRUZ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Nidia Esperanza Herrera Padilla</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>ALSACIA RESERVADO</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>2026-02-12, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2108,7 +2050,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LINZ E1</t>
+          <t>LA PALMA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2119,7 +2061,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2137,8 +2079,16 @@
       <c r="P21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-28</t>
+        </is>
+      </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
@@ -2162,54 +2112,100 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LOIRA CIUDAD LA SALLE</t>
+          <t>LA PEÑA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jose Alejandro Barcenas Moreno</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2220,7 +2216,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LORCA</t>
+          <t>LA SCALA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2236,13 +2232,13 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Johanna Diaz Mora</t>
+          <t>Javier Manuel Gonzalez Angulo</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>LA SCALA</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2252,17 +2248,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2272,7 +2268,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O23" t="n">
@@ -2283,35 +2279,35 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-19, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-20</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="U23" t="n">
         <v>4</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2322,12 +2318,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LYON 2 CIUDAD LA SALLE</t>
+          <t>LA TERRA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2336,40 +2332,76 @@
           <t>Pedro Mora</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nidia Esperanza Herrera Padilla</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ALSACIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>2026-02-12, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25">
@@ -2380,7 +2412,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LYON CIUDAD LA SALLE</t>
+          <t>LINZ E1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2409,11 +2441,7 @@
       <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
@@ -2438,7 +2466,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MALAGA CASTILLA RESERVADO</t>
+          <t>LOIRA CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2449,16 +2477,12 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -2473,14 +2497,10 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="n">
@@ -2504,7 +2524,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
+          <t>LORCA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2515,28 +2535,28 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yorleynis Montejo Ruiz</t>
+          <t>Johanna Diaz Mora</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2546,12 +2566,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2567,35 +2587,35 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-13, 2026-02-19, 2026-02-20</t>
         </is>
       </c>
       <c r="U27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="28">
@@ -2606,12 +2626,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MONTPELLIER CIUDAD LA SALLE</t>
+          <t>LYON 2 CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2620,76 +2640,40 @@
           <t>Pedro Mora</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Juan Alberto Gutierrez Forero</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2700,7 +2684,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PASEO DE SEVILLA</t>
+          <t>LYON CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2711,7 +2695,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -2731,14 +2715,10 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="n">
@@ -2762,12 +2742,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PASEO SAN RAFAEL</t>
+          <t>MALAGA CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2776,80 +2756,48 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Yuli Maribel Arias Cifuentes</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
-        </is>
-      </c>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2860,50 +2808,98 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PEÑAZUL EL POBLADO</t>
+          <t>METROPOLI 30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Yorleynis Montejo Ruiz</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>METROPOLI 30</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2914,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PEÑON DE ALICANTE</t>
+          <t>MONTPELLIER CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2925,48 +2921,40 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jennifer Paola Lopez Vaca</t>
+          <t>Juan Alberto Gutierrez Forero</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>LUNES</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -2977,93 +2965,125 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
+          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+          <t>2026-02-05, 2026-02-19, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-02-11, 2026-02-17, 2026-02-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="U32" t="n">
         <v>4</v>
       </c>
       <c r="V32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PROVENZA PRESTIGE</t>
+          <t>PARKSIDE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>José Luis Suarez</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ivan Barbosa</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+          <t>2026-02-05, 2026-02-23</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-23</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11</t>
+        </is>
+      </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -3074,53 +3094,45 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PRUEBA</t>
+          <t>PASEO DE SEVILLA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PRUEBA</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>SABADO</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2026-02-07, 2026-02-09, 2026-02-14, 2026-02-16, 2026-02-21, 2026-02-23, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
+        </is>
+      </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="n">
@@ -3139,12 +3151,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BARRANQUILLA</t>
+          <t xml:space="preserve">BOGOTA </t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PUERTA DORADA CRISTALINA</t>
+          <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3155,28 +3167,28 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Germán Baquero</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kelly Gutierrez</t>
+          <t>Yuli Maribel Arias Cifuentes</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>PUERTA DORADA</t>
+          <t>ZIPAQUIRA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>MARTES</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3184,14 +3196,10 @@
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3207,129 +3215,89 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-18, 2026-02-23</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
+        </is>
+      </c>
       <c r="U35" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BARRANQUILLA</t>
+          <t xml:space="preserve">BOGOTA </t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RIVERBAY</t>
+          <t>PEÑAZUL EL POBLADO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>José Luis Suarez</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Orlando Iguaran</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>02:00:00</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-05, 2026-02-18, 2026-02-24, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-18, 2026-02-26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3340,7 +3308,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3351,50 +3319,50 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Jhon Alexander Guarin Reina</t>
+          <t>Jennifer Paola Lopez Vaca</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CIUDAD LA SALLE</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
       <c r="O37" t="n">
         <v>4</v>
       </c>
@@ -3403,32 +3371,32 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-10, 2026-02-11, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="U37" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V37" t="n">
         <v>4</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="X37" t="n">
         <v>1</v>
@@ -3442,7 +3410,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>PROVENZA PRESTIGE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3453,7 +3421,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -3473,14 +3441,10 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="n">
@@ -3504,7 +3468,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>PRUEBA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3515,98 +3479,66 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Zuri Andreina Orduz Sepulveda</t>
-        </is>
-      </c>
+          <t>PRUEBA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
+          <t>SABADO</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-07, 2026-02-09, 2026-02-14, 2026-02-16, 2026-02-21, 2026-02-23, 2026-02-28</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
         <v>4</v>
       </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>2026-02-11, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>PUERTA DORADA ARRECIFE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3617,30 +3549,22 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Germán Baquero</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Yuli Maribel Arias Cifuentes</t>
+          <t>Tatiana Navarro</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>VIERNES</t>
@@ -3649,7 +3573,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3665,94 +3589,130 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-25</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="U40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V40" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W40" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>PUERTA DORADA CRISTALINA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>Germán Baquero</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kelly Gutierrez</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>PUERTA DORADA</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2026-02-03, 2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
+          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-18, 2026-02-23</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-20, 2026-02-26</t>
+        </is>
+      </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3761,12 +3721,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>PUERTA DORADA MARISMA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3777,113 +3737,87 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Germán Baquero</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dario Acosta Rubiano</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
+          <t>Carlos Quiroz</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+          <t>SABADO</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-07, 2026-02-09, 2026-02-14, 2026-02-16, 2026-02-21, 2026-02-23, 2026-02-28</t>
         </is>
       </c>
       <c r="O42" t="n">
         <v>4</v>
       </c>
       <c r="P42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-28</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2026-02-07, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="U42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="X42" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOGOTA </t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Entregas</t>
-        </is>
-      </c>
+          <t>PUERTA DORADA NATURA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
@@ -3893,14 +3827,18 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-27</t>
+        </is>
+      </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="n">
@@ -3909,22 +3847,18 @@
       <c r="V43" t="n">
         <v>0</v>
       </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t xml:space="preserve">PUERTA DORADA NATURA </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3935,40 +3869,28 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Germán Baquero</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mauricio Andres Cervantes</t>
+          <t>Lina Olarte</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>TRES QUEBRADAS</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
@@ -3976,7 +3898,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -3985,48 +3907,32 @@
       <c r="P44" t="n">
         <v>4</v>
       </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-26</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>RIVERBAY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4037,48 +3943,44 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>José Luis Suarez</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leonardo de Jesus Guerrero Cabrera</t>
+          <t>Orlando Iguaran</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>MARTES</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -4089,46 +3991,46 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-03, 2026-02-05, 2026-02-18, 2026-02-24, 2026-02-26</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2026-02-14, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-18, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="U45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="V45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W45" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="X45" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ZURI - ZENTRAL</t>
+          <t>RIVERBLUE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4139,20 +4041,16 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>José Luis Suarez</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yenny Paola Munevar Peña</t>
+          <t>Jeeniffer Perez</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>ZENTRAL</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>JUEVES</t>
@@ -4183,34 +4081,916 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>7</v>
+      </c>
+      <c r="V46" t="n">
+        <v>6</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Jhon Alexander Guarin Reina</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>4</v>
+      </c>
+      <c r="P47" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>8</v>
+      </c>
+      <c r="V47" t="n">
+        <v>4</v>
+      </c>
+      <c r="W47" t="n">
+        <v>2</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SAN LUCAS LA QUINTA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SAN MATEO - LA QUINTA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Zuri Andreina Orduz Sepulveda</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>4</v>
+      </c>
+      <c r="P49" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-10, 2026-02-11, 2026-02-18, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2026-02-12, 2026-02-18, 2026-02-19</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
+        <v>5</v>
+      </c>
+      <c r="V49" t="n">
+        <v>3</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SAN SEBASTIAN LA QUINTA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>4</v>
+      </c>
+      <c r="P50" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-12, 2026-02-19, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
+        <v>5</v>
+      </c>
+      <c r="V50" t="n">
+        <v>5</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SAN SIMON LA QUINTA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Dario Acosta Rubiano</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>4</v>
+      </c>
+      <c r="P52" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-19, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
+        <v>4</v>
+      </c>
+      <c r="V52" t="n">
+        <v>6</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>URBANISMO TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mauricio Andres Cervantes</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>4</v>
+      </c>
+      <c r="P54" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
+        <v>4</v>
+      </c>
+      <c r="V54" t="n">
+        <v>3</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Leonardo de Jesus Guerrero Cabrera</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>4</v>
+      </c>
+      <c r="P55" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
+        <v>6</v>
+      </c>
+      <c r="V55" t="n">
+        <v>6</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ZURI - ZENTRAL</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Yenny Paola Munevar Peña</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ZENTRAL</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>4</v>
+      </c>
+      <c r="P56" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
         <is>
           <t>2026-02-13, 2026-02-27</t>
         </is>
       </c>
-      <c r="U46" t="n">
-        <v>4</v>
-      </c>
-      <c r="V46" t="n">
+      <c r="U56" t="n">
+        <v>5</v>
+      </c>
+      <c r="V56" t="n">
         <v>2</v>
       </c>
-      <c r="W46" t="n">
-        <v>1</v>
-      </c>
-      <c r="X46" t="n">
+      <c r="W56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X56" t="n">
         <v>0.5</v>
       </c>
     </row>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -682,20 +682,20 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U3" t="n">
         <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -899,25 +899,25 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23, 2026-02-24</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25</t>
+          <t>2026-02-05, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1159,25 +1159,25 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10</t>
+          <t>2026-02-02, 2026-02-09</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X10" t="n">
         <v>1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.25</v>
       </c>
     </row>
     <row r="11">
@@ -1436,20 +1436,20 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-12, 2026-02-26</t>
         </is>
       </c>
       <c r="U13" t="n">
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W13" t="n">
         <v>0.25</v>
       </c>
       <c r="X13" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
@@ -1533,25 +1533,25 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-16, 2026-02-17</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-16</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="U16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
         <v>3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
         <v>0.75</v>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -1878,13 +1878,13 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
         <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X18" t="n">
         <v>0.25</v>
@@ -1967,25 +1967,25 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-27</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-02-27, 2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X19" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="20">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V24" t="n">
         <v>2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="X24" t="n">
         <v>0.5</v>
@@ -2597,25 +2597,25 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-13, 2026-02-19, 2026-02-20</t>
+          <t>2026-02-05, 2026-02-13, 2026-02-19</t>
         </is>
       </c>
       <c r="U27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="28">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -2890,13 +2890,13 @@
         </is>
       </c>
       <c r="U31" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V31" t="n">
         <v>4</v>
       </c>
       <c r="W31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
         <v>1</v>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-19, 2026-02-20, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="U32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V32" t="n">
         <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X32" t="n">
         <v>0.25</v>
@@ -3070,20 +3070,20 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11</t>
+          <t>2026-02-03, 2026-02-10</t>
         </is>
       </c>
       <c r="U33" t="n">
         <v>1</v>
       </c>
       <c r="V33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W33" t="n">
         <v>0.25</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-25</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -3234,13 +3234,13 @@
         </is>
       </c>
       <c r="U35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V35" t="n">
         <v>3</v>
       </c>
       <c r="W35" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>0.75</v>
@@ -3381,25 +3381,25 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-02-10, 2026-02-11, 2026-02-17, 2026-02-24</t>
+          <t>2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="U37" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W37" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="38">
@@ -3599,25 +3599,25 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V40" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W40" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -3701,18 +3701,18 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-20, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27, 2026-02-28</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -3796,13 +3796,13 @@
         </is>
       </c>
       <c r="U42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
         <v>3</v>
       </c>
       <c r="W42" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="X42" t="n">
         <v>1</v>
@@ -4001,25 +4001,25 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-18, 2026-02-24</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-18, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-04, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="U45" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W45" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="46">
@@ -4091,25 +4091,25 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U46" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W46" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -4202,13 +4202,13 @@
         </is>
       </c>
       <c r="U47" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V47" t="n">
         <v>4</v>
       </c>
       <c r="W47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X47" t="n">
         <v>1</v>
@@ -4357,25 +4357,25 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-10, 2026-02-11, 2026-02-18, 2026-02-24</t>
+          <t>2026-02-04, 2026-02-10, 2026-02-18, 2026-02-24</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-18, 2026-02-19</t>
+          <t>2026-02-12, 2026-02-18</t>
         </is>
       </c>
       <c r="U49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W49" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50">
@@ -4455,25 +4455,25 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-12, 2026-02-19, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W50" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="X50" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -4626,20 +4626,20 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-19, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="U52" t="n">
         <v>4</v>
       </c>
       <c r="V52" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W52" t="n">
         <v>1</v>
       </c>
       <c r="X52" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -4782,20 +4782,20 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-26</t>
         </is>
       </c>
       <c r="U54" t="n">
         <v>4</v>
       </c>
       <c r="V54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="55">
@@ -4879,25 +4879,25 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U55" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V55" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W55" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="X55" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="56">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -4982,13 +4982,13 @@
         </is>
       </c>
       <c r="U56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V56" t="n">
         <v>2</v>
       </c>
       <c r="W56" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="X56" t="n">
         <v>0.5</v>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X56"/>
+  <dimension ref="A1:X55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3809,26 +3809,62 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>PUERTA DORADA NATURA</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Germán Baquero</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lina Olarte</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>4</v>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
@@ -3839,16 +3875,28 @@
           <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-27</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3858,7 +3906,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">PUERTA DORADA NATURA </t>
+          <t>RIVERBAY</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3869,36 +3917,44 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Germán Baquero</t>
+          <t>José Luis Suarez</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lina Olarte</t>
+          <t>Orlando Iguaran</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -3907,21 +3963,37 @@
       <c r="P44" t="n">
         <v>4</v>
       </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-05, 2026-02-18, 2026-02-24, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-10, 2026-02-18, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="45">
@@ -3932,7 +4004,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RIVERBAY</t>
+          <t>RIVERBLUE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3948,39 +4020,31 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orlando Iguaran</t>
+          <t>Jeeniffer Perez</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>02:00:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -3991,46 +4055,46 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-05, 2026-02-18, 2026-02-24, 2026-02-26</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-18, 2026-02-24</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U45" t="n">
         <v>4</v>
       </c>
       <c r="V45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W45" t="n">
         <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BARRANQUILLA</t>
+          <t xml:space="preserve">BOGOTA </t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RIVERBLUE</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4041,38 +4105,50 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>José Luis Suarez</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jeeniffer Perez</t>
+          <t>Jhon Alexander Guarin Reina</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
       <c r="O46" t="n">
         <v>4</v>
       </c>
@@ -4081,22 +4157,22 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
+          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U46" t="n">
@@ -4120,98 +4196,58 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Jhon Alexander Guarin Reina</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
       <c r="U47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4222,12 +4258,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4236,44 +4272,84 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Zuri Andreina Orduz Sepulveda</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
+          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-10, 2026-02-18, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2026-02-12, 2026-02-18</t>
+        </is>
+      </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="49">
@@ -4284,7 +4360,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4300,7 +4376,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zuri Andreina Orduz Sepulveda</t>
+          <t>Yuli Maribel Arias Cifuentes</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -4311,32 +4387,28 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O49" t="n">
@@ -4347,35 +4419,35 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-10, 2026-02-18, 2026-02-24</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-18</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U49" t="n">
         <v>4</v>
       </c>
       <c r="V49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W49" t="n">
         <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -4386,12 +4458,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4400,80 +4472,44 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Yuli Maribel Arias Cifuentes</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4484,58 +4520,100 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Dario Acosta Rubiano</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -4546,100 +4624,50 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Dario Acosta Rubiano</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
       <c r="U52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4650,12 +4678,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4664,36 +4692,84 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mauricio Andres Cervantes</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-26</t>
+        </is>
+      </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="54">
@@ -4704,7 +4780,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4720,13 +4796,13 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mauricio Andres Cervantes</t>
+          <t>Leonardo de Jesus Guerrero Cabrera</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>TRES QUEBRADAS</t>
+          <t>NORTE</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4736,17 +4812,17 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4756,7 +4832,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O54" t="n">
@@ -4767,35 +4843,35 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-26</t>
+          <t>2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U54" t="n">
         <v>4</v>
       </c>
       <c r="V54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="55">
@@ -4806,7 +4882,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>ZURI - ZENTRAL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4817,18 +4893,18 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leonardo de Jesus Guerrero Cabrera</t>
+          <t>Yenny Paola Munevar Peña</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>NORTE</t>
+          <t>ZENTRAL</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4836,21 +4912,13 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
@@ -4869,128 +4937,34 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-13, 2026-02-27</t>
         </is>
       </c>
       <c r="U55" t="n">
         <v>4</v>
       </c>
       <c r="V55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W55" t="n">
         <v>1</v>
       </c>
       <c r="X55" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOGOTA </t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>ZURI - ZENTRAL</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Yenny Paola Munevar Peña</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>ZENTRAL</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="O56" t="n">
-        <v>4</v>
-      </c>
-      <c r="P56" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>2026-02-13, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="U56" t="n">
-        <v>4</v>
-      </c>
-      <c r="V56" t="n">
-        <v>2</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1</v>
-      </c>
-      <c r="X56" t="n">
         <v>0.5</v>
       </c>
     </row>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X55"/>
+  <dimension ref="A1:X54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,26 +983,66 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>C DEL PARQUE TAYRONA APTOS</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Germán Baquero</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Carlos Sandoval</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CIUDAD DEL PARQUE</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JUEVES </t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4</v>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>2026-02-21, 2026-02-26</t>
@@ -1013,16 +1053,28 @@
           <t>2026-02-13, 2026-02-21, 2026-02-27</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-02-20, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1188,7 +1240,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CIUDAD DEL PARQUE TAYRONA APTOS</t>
+          <t>DIMARO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1199,40 +1251,36 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Germán Baquero</t>
+          <t>José Luis Suarez</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Carlos Sandoval</t>
+          <t xml:space="preserve">Julio Curvelo </t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>CIUDAD DEL PARQUE</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUEVES </t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1241,32 +1289,48 @@
       <c r="P11" t="n">
         <v>4</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BARRANQUILLA</t>
+          <t xml:space="preserve">BOGOTA </t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DIMARO</t>
+          <t>EL CAMPO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1277,36 +1341,50 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>José Luis Suarez</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Julio Curvelo </t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+          <t>Juan Sebastian Ardila Castañeda</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1317,35 +1395,35 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-12, 2026-02-26</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
@@ -1356,7 +1434,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EL CAMPO</t>
+          <t>EL CASTELL IBERIA RESERVADO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1372,45 +1450,43 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Juan Sebastian Ardila Castañeda</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
+          <t>Doriam Mayreth Sanchez Saenz</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>TRES QUEBRADAS</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>LUNES</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1421,35 +1497,35 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-26</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-16</t>
         </is>
       </c>
       <c r="U13" t="n">
+        <v>4</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4</v>
+      </c>
+      <c r="W13" t="n">
         <v>1</v>
       </c>
-      <c r="V13" t="n">
-        <v>2</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.25</v>
-      </c>
       <c r="X13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1460,167 +1536,155 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EL CASTELL IBERIA RESERVADO</t>
+          <t>GALLET CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Doriam Mayreth Sanchez Saenz</t>
-        </is>
-      </c>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-16</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GALLET CIUDAD LA SALLE</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>José Luis Suarez</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Erich Camargo</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BARRANQUILLA</t>
+          <t xml:space="preserve">BOGOTA </t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>IZOLA ZENTRAL-CITIZZEN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1631,38 +1695,42 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>José Luis Suarez</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Erich Camargo</t>
+          <t>Maicol David Sanchez Ortiz</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ZENTRAL</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
       <c r="O16" t="n">
         <v>4</v>
       </c>
@@ -1671,35 +1739,35 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="U16" t="n">
         <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="17">
@@ -1710,7 +1778,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IZOLA ZENTRAL-CITIZZEN</t>
+          <t>LA ALMERIA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1726,35 +1794,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maicol David Sanchez Ortiz</t>
+          <t>Nidia Esperanza Herrera Padilla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ZENTRAL</t>
+          <t>ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1765,32 +1833,32 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
         <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X17" t="n">
         <v>0.25</v>
@@ -1804,7 +1872,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LA ALMERIA ALSACIA RESERVADO</t>
+          <t>LA CABRERA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1815,18 +1883,18 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nidia Esperanza Herrera Padilla</t>
+          <t>Martin Rafael Bohorquez Marrugo</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ALSACIA RESERVADO</t>
+          <t>TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1834,7 +1902,11 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>VIERNES</t>
@@ -1859,17 +1931,17 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-28</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2026-02-26, 2026-02-28</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-27</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -1878,13 +1950,13 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X18" t="n">
         <v>0.25</v>
@@ -1898,12 +1970,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LA CABRERA</t>
+          <t>LA CRUZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1912,80 +1984,36 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Martin Rafael Bohorquez Marrugo</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>TRES QUEBRADAS</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>2026-02-26, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1996,7 +2024,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LA CRUZ</t>
+          <t>LA PALMA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2025,8 +2053,16 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-28</t>
+        </is>
+      </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="n">
@@ -2050,12 +2086,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LA PALMA</t>
+          <t>LA PEÑA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -2064,44 +2100,86 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Jose Alejandro Barcenas Moreno</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
+          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2112,7 +2190,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LA PEÑA</t>
+          <t>LA SCALA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2128,15 +2206,13 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jose Alejandro Barcenas Moreno</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
+          <t>Javier Manuel Gonzalez Angulo</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>TRES QUEBRADAS</t>
+          <t>LA SCALA</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2146,17 +2222,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2166,7 +2242,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -2177,22 +2253,22 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="U22" t="n">
@@ -2216,7 +2292,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LA SCALA</t>
+          <t>LA TERRA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2227,48 +2303,40 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Javier Manuel Gonzalez Angulo</t>
+          <t>Nidia Esperanza Herrera Padilla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>LA SCALA</t>
+          <t>ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O23" t="n">
@@ -2279,35 +2347,35 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24">
@@ -2318,12 +2386,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LA TERRA ALSACIA RESERVADO</t>
+          <t>LINZ E1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2332,76 +2400,36 @@
           <t>Pedro Mora</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Nidia Esperanza Herrera Padilla</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>ALSACIA RESERVADO</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2412,7 +2440,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LINZ E1</t>
+          <t>LOIRA CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2441,7 +2469,11 @@
       <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
@@ -2466,54 +2498,98 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LOIRA CIUDAD LA SALLE</t>
+          <t>LORCA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Johanna Diaz Mora</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-19, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-13, 2026-02-19</t>
+        </is>
+      </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="27">
@@ -2524,98 +2600,54 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LORCA</t>
+          <t>LYON 2 CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Johanna Diaz Mora</t>
-        </is>
-      </c>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>15:00:00</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-19, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-13, 2026-02-19</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2626,7 +2658,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LYON 2 CIUDAD LA SALLE</t>
+          <t>LYON CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2684,7 +2716,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LYON CIUDAD LA SALLE</t>
+          <t>MALAGA CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2695,12 +2727,16 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -2715,10 +2751,14 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="n">
@@ -2742,62 +2782,98 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MALAGA CASTILLA RESERVADO</t>
+          <t>METROPOLI 30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Yorleynis Montejo Ruiz</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>METROPOLI 30</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2808,7 +2884,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
+          <t>MONTPELLIER CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2824,43 +2900,35 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yorleynis Montejo Ruiz</t>
+          <t>Juan Alberto Gutierrez Forero</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
+          <t>CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -2871,46 +2939,46 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24</t>
+          <t>2026-02-05, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="U31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MONTPELLIER CIUDAD LA SALLE</t>
+          <t>PARKSIDE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2921,40 +2989,36 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>José Luis Suarez</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Juan Alberto Gutierrez Forero</t>
+          <t>Ivan Barbosa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>LUNES</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>MARTES</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -2965,125 +3029,97 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-23</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-23</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-03, 2026-02-10</t>
         </is>
       </c>
       <c r="U32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W32" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="X32" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BARRANQUILLA</t>
+          <t xml:space="preserve">BOGOTA </t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PARKSIDE</t>
+          <t>PASEO DE SEVILLA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>José Luis Suarez</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Ivan Barbosa</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-23</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-23</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-10</t>
-        </is>
-      </c>
+          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3094,12 +3130,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PASEO DE SEVILLA</t>
+          <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -3108,44 +3144,80 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
+        </is>
+      </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="35">
@@ -3156,12 +3228,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PASEO SAN RAFAEL</t>
+          <t>PEÑAZUL EL POBLADO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3170,80 +3242,36 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Yuli Maribel Arias Cifuentes</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3254,12 +3282,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PEÑAZUL EL POBLADO</t>
+          <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3268,36 +3296,84 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Jennifer Paola Lopez Vaca</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026-02-10, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="37">
@@ -3308,98 +3384,54 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PEÑON DE ALICANTE</t>
+          <t>PROVENZA PRESTIGE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Jennifer Paola Lopez Vaca</t>
-        </is>
-      </c>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2026-02-10, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3410,40 +3442,52 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PROVENZA PRESTIGE</t>
+          <t>PRUEBA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
+          <t>PRUEBA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SABADO</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-02-07, 2026-02-09, 2026-02-14, 2026-02-16, 2026-02-21, 2026-02-23, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+        </is>
+      </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
@@ -3463,12 +3507,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOGOTA </t>
+          <t>BARRANQUILLA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PRUEBA</t>
+          <t>PUERTA DORADA ARRECIFE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3479,55 +3523,75 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PRUEBA</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>Germán Baquero</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tatiana Navarro</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SABADO</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LUNES</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-09, 2026-02-14, 2026-02-16, 2026-02-21, 2026-02-23, 2026-02-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
         <v>4</v>
       </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -3538,7 +3602,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PUERTA DORADA ARRECIFE</t>
+          <t>PUERTA DORADA CRISTALINA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3554,23 +3618,35 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tatiana Navarro</t>
+          <t>Kelly Gutierrez</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>PUERTA DORADA</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
@@ -3589,35 +3665,31 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-03, 2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-18, 2026-02-23</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="n">
         <v>4</v>
       </c>
       <c r="V40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3628,7 +3700,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PUERTA DORADA CRISTALINA</t>
+          <t>PUERTA DORADA MARISMA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3644,78 +3716,70 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kelly Gutierrez</t>
+          <t>Carlos Quiroz</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>PUERTA DORADA</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
+          <t>SABADO</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-02-07, 2026-02-09, 2026-02-14, 2026-02-16, 2026-02-21, 2026-02-23, 2026-02-28</t>
         </is>
       </c>
       <c r="O41" t="n">
         <v>4</v>
       </c>
       <c r="P41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-28</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-18, 2026-02-23</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2026-02-07, 2026-02-21, 2026-02-28</t>
+        </is>
+      </c>
       <c r="U41" t="n">
         <v>4</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W41" t="n">
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -3726,7 +3790,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PUERTA DORADA MARISMA</t>
+          <t>PUERTA DORADA NATURA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3742,64 +3806,64 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Carlos Quiroz</t>
+          <t>Lina Olarte</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>SABADO</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>2026-02-07, 2026-02-09, 2026-02-14, 2026-02-16, 2026-02-21, 2026-02-23, 2026-02-28</t>
-        </is>
-      </c>
       <c r="O42" t="n">
         <v>4</v>
       </c>
       <c r="P42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-28</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-27</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
           <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>2026-02-07, 2026-02-21, 2026-02-28</t>
-        </is>
-      </c>
       <c r="U42" t="n">
         <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W42" t="n">
         <v>1</v>
@@ -3816,7 +3880,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PUERTA DORADA NATURA</t>
+          <t>RIVERBAY</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3827,36 +3891,44 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Germán Baquero</t>
+          <t>José Luis Suarez</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lina Olarte</t>
+          <t>Orlando Iguaran</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O43" t="n">
@@ -3867,35 +3939,35 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-27</t>
+          <t>2026-02-03, 2026-02-05, 2026-02-18, 2026-02-24, 2026-02-26</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-18, 2026-02-24</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="U43" t="n">
         <v>4</v>
       </c>
       <c r="V43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="44">
@@ -3906,7 +3978,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RIVERBAY</t>
+          <t>RIVERBLUE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3922,39 +3994,31 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orlando Iguaran</t>
+          <t>Jeeniffer Perez</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>02:00:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -3965,46 +4029,46 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-05, 2026-02-18, 2026-02-24, 2026-02-26</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-18, 2026-02-24</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U44" t="n">
         <v>4</v>
       </c>
       <c r="V44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W44" t="n">
         <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BARRANQUILLA</t>
+          <t xml:space="preserve">BOGOTA </t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RIVERBLUE</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4015,38 +4079,50 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>José Luis Suarez</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jeeniffer Perez</t>
+          <t>Jhon Alexander Guarin Reina</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
       <c r="O45" t="n">
         <v>4</v>
       </c>
@@ -4055,22 +4131,22 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
+          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U45" t="n">
@@ -4094,98 +4170,58 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Jhon Alexander Guarin Reina</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -4196,12 +4232,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -4210,44 +4246,84 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Zuri Andreina Orduz Sepulveda</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
+          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-10, 2026-02-18, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-02-12, 2026-02-18</t>
+        </is>
+      </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48">
@@ -4258,7 +4334,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4274,7 +4350,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Zuri Andreina Orduz Sepulveda</t>
+          <t>Yuli Maribel Arias Cifuentes</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -4285,32 +4361,28 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -4321,35 +4393,35 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-10, 2026-02-18, 2026-02-24</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-18</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U48" t="n">
         <v>4</v>
       </c>
       <c r="V48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W48" t="n">
         <v>1</v>
       </c>
       <c r="X48" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -4360,12 +4432,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4374,80 +4446,44 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Yuli Maribel Arias Cifuentes</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>ZIPAQUIRA</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4458,58 +4494,100 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Dario Acosta Rubiano</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -4520,100 +4598,50 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Dario Acosta Rubiano</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4624,12 +4652,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Entregas</t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4638,36 +4666,84 @@
           <t>Ronald Forero</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mauricio Andres Cervantes</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-26</t>
+        </is>
+      </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="53">
@@ -4678,7 +4754,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4694,13 +4770,13 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mauricio Andres Cervantes</t>
+          <t>Leonardo de Jesus Guerrero Cabrera</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>TRES QUEBRADAS</t>
+          <t>NORTE</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4710,17 +4786,17 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4730,7 +4806,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O53" t="n">
@@ -4741,35 +4817,35 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-26</t>
+          <t>2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="U53" t="n">
         <v>4</v>
       </c>
       <c r="V53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="54">
@@ -4780,7 +4856,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>ZURI - ZENTRAL</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4791,18 +4867,18 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ronald Forero</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Leonardo de Jesus Guerrero Cabrera</t>
+          <t>Yenny Paola Munevar Peña</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>NORTE</t>
+          <t>ZENTRAL</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4810,21 +4886,13 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
@@ -4843,128 +4911,34 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-13, 2026-02-27</t>
         </is>
       </c>
       <c r="U54" t="n">
         <v>4</v>
       </c>
       <c r="V54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOGOTA </t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>ZURI - ZENTRAL</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Yenny Paola Munevar Peña</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>ZENTRAL</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="O55" t="n">
-        <v>4</v>
-      </c>
-      <c r="P55" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>2026-02-13, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="U55" t="n">
-        <v>4</v>
-      </c>
-      <c r="V55" t="n">
-        <v>2</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1</v>
-      </c>
-      <c r="X55" t="n">
         <v>0.5</v>
       </c>
     </row>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -2586,7 +2586,7 @@
         <v>3</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
         <v>0.75</v>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -577,12 +577,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2022-11-21, 2022-11-28, 2022-12-06, 2022-12-13, 2022-12-20, 2022-12-21, 2023-01-03, 2023-01-10, 2023-01-17, 2023-01-24, 2023-01-31, 2023-02-08, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-18, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-22, 2023-08-29, 2023-09-06, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-16, 2024-03-21, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-11, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-05, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-06, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-02, 2024-09-04, 2024-09-12, 2024-09-18, 2024-09-26, 2024-10-02, 2024-10-11, 2024-10-17, 2024-10-24, 2025-12-26, 2025-12-29, 2025-12-30, 2026-01-02, 2026-01-05, 2026-01-06, 2026-01-08, 2026-01-13, 2026-01-29, 2026-01-30, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18, 2026-03-03</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2022-11-25, 2022-12-01, 2022-12-09, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-07, 2023-09-13, 2023-09-20, 2023-09-28, 2023-10-05, 2023-10-11, 2023-10-18, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-25, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-04, 2024-01-11, 2024-01-19, 2024-01-29, 2024-02-02, 2024-02-09, 2024-02-17, 2024-02-23, 2024-03-01, 2024-03-08, 2024-03-18, 2024-03-22, 2024-04-04, 2024-04-13, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-11, 2024-05-17, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-05, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-30, 2024-09-02, 2024-09-06, 2024-09-16, 2024-09-20, 2024-09-28, 2024-10-03, 2024-10-16, 2024-10-18, 2024-10-25, 2025-12-26, 2025-12-29, 2026-01-02, 2026-01-05, 2026-01-06, 2026-01-08, 2026-01-13, 2026-01-29, 2026-01-30, 2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-03-03, 2026-03-04</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -639,12 +639,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2025-12-23, 2025-12-26, 2026-01-06, 2026-01-23, 2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2025-12-26, 2026-01-06, 2026-01-23, 2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -699,11 +699,7 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -791,12 +787,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2023-08-10, 2023-08-18, 2023-08-25, 2023-08-31, 2023-09-01, 2023-09-04, 2023-09-08, 2023-09-18, 2023-10-04, 2023-10-20, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-12, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-05, 2024-06-13, 2024-06-20, 2024-06-28, 2024-07-05, 2024-07-09, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-14, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-06, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-07, 2024-12-16, 2025-01-07, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-28, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-30, 2025-05-06, 2025-05-12, 2025-05-21, 2025-05-26, 2025-05-29, 2025-06-04, 2025-06-12, 2025-06-16, 2025-06-25, 2025-07-01, 2025-07-07, 2025-07-14, 2025-07-21, 2025-07-28, 2025-08-04, 2025-08-11, 2025-08-20, 2025-08-25, 2025-09-01, 2025-09-08, 2025-09-15, 2025-09-22, 2025-09-30, 2025-10-06, 2025-10-14, 2025-10-20, 2025-10-28, 2025-11-04, 2025-11-10, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-03, 2025-12-11, 2025-12-15, 2025-12-22, 2026-01-05, 2026-01-13, 2026-01-19, 2026-01-26, 2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23, 2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2023-08-11, 2023-08-24, 2023-08-30, 2023-08-31, 2023-09-01, 2023-09-04, 2023-09-05, 2023-09-18, 2023-10-04, 2023-10-20, 2023-11-23, 2023-11-30, 2023-12-06, 2023-12-11, 2023-12-18, 2024-01-12, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-21, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-12, 2024-04-19, 2024-05-02, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-06, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-05, 2024-07-09, 2024-07-12, 2024-07-13, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-09, 2024-10-16, 2024-10-21, 2024-10-28, 2024-11-06, 2024-11-15, 2024-11-20, 2024-11-28, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-09, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-11, 2025-03-17, 2025-03-28, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-30, 2025-05-06, 2025-05-13, 2025-05-21, 2025-05-26, 2025-06-04, 2025-06-12, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-16, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-21, 2025-09-01, 2025-09-03, 2025-09-12, 2025-09-18, 2025-09-24, 2025-10-01, 2025-10-10, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-06, 2025-11-12, 2025-11-21, 2025-11-26, 2025-12-03, 2025-12-05, 2025-12-12, 2025-12-17, 2025-12-30, 2026-01-07, 2026-01-14, 2026-01-21, 2026-01-30, 2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25, 2026-03-04, 2026-03-11</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -861,12 +857,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2022-11-17, 2022-11-29, 2022-12-02, 2022-12-09, 2022-12-15, 2022-12-21, 2022-12-28, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-09, 2023-02-23, 2023-03-09, 2023-03-23, 2023-04-13, 2023-04-20, 2023-05-04, 2023-05-06, 2023-05-11, 2023-05-18, 2023-06-01, 2023-06-15, 2023-06-29, 2023-07-13, 2023-07-22, 2023-07-27, 2023-08-10, 2023-08-12, 2023-08-24, 2023-09-07, 2023-09-22, 2023-10-06, 2023-10-20, 2023-11-02, 2023-11-14, 2023-11-17, 2023-11-30, 2023-12-07, 2023-12-18, 2023-12-26, 2025-12-22, 2025-12-26, 2026-01-06, 2026-02-02, 2026-02-04, 2026-02-10, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25, 2026-03-02, 2026-03-03</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2022-11-28, 2022-12-02, 2022-12-09, 2022-12-16, 2022-12-22, 2022-12-29, 2023-01-06, 2023-01-14, 2023-01-21, 2023-01-27, 2023-02-10, 2023-02-25, 2023-03-11, 2023-03-25, 2023-04-15, 2023-04-22, 2023-05-06, 2023-05-12, 2023-05-20, 2023-06-03, 2023-06-17, 2023-07-01, 2023-07-15, 2023-07-24, 2023-07-29, 2023-08-12, 2023-08-19, 2023-08-26, 2023-09-09, 2023-09-23, 2023-10-07, 2023-10-20, 2023-11-07, 2023-11-14, 2023-11-17, 2023-11-30, 2023-12-07, 2023-12-18, 2025-12-22, 2025-12-26, 2026-01-06, 2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25, 2026-03-02, 2026-03-03</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -921,16 +917,8 @@
       <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2021-12-28, 2021-12-29, 2022-01-06, 2022-01-11, 2022-01-18, 2022-01-25, 2022-02-01, 2022-02-08, 2022-02-11, 2022-02-16, 2022-02-23, 2022-02-28, 2022-03-09, 2022-03-10, 2022-03-15, 2022-03-22, 2022-03-30, 2022-04-06, 2022-04-13, 2022-04-20, 2022-04-28, 2022-05-07, 2022-05-18, 2022-05-19, 2022-05-24, 2022-06-02, 2022-06-08, 2022-06-17, 2022-06-22, 2022-06-28, 2022-07-05, 2022-07-12, 2022-07-19, 2022-07-26, 2022-08-02, 2022-08-09, 2022-08-16, 2022-08-23, 2022-08-30, 2022-09-06, 2022-09-13, 2022-09-20, 2022-09-27, 2022-10-04, 2022-10-11, 2022-10-18, 2022-10-25, 2022-11-01, 2022-11-08, 2022-11-15, 2022-11-22, 2022-11-29, 2022-12-06, 2022-12-13, 2022-12-20, 2022-12-27, 2023-01-03, 2023-01-10, 2023-01-17, 2023-01-23, 2023-01-30, 2023-02-06, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-18, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2024-01-04, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2025-11-27, 2025-11-28</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>2021-12-28, 2021-12-30, 2022-01-07, 2022-01-18, 2022-01-19, 2022-02-02, 2022-02-03, 2022-02-11, 2022-02-16, 2022-02-23, 2022-02-28, 2022-03-09, 2022-03-10, 2022-03-22, 2022-03-23, 2022-03-29, 2022-04-06, 2022-04-13, 2022-04-20, 2022-04-27, 2022-05-04, 2022-05-11, 2022-05-18, 2022-05-24, 2022-05-25, 2022-06-02, 2022-06-08, 2022-06-21, 2022-06-23, 2022-06-29, 2022-07-05, 2022-07-13, 2022-07-21, 2022-07-27, 2022-08-03, 2022-08-10, 2022-08-17, 2022-08-25, 2022-09-01, 2022-09-07, 2022-09-14, 2022-09-21, 2022-09-27, 2022-10-05, 2022-10-12, 2022-10-20, 2022-10-26, 2022-11-02, 2022-11-10, 2022-11-16, 2022-11-24, 2022-12-01, 2022-12-07, 2022-12-14, 2022-12-20, 2022-12-28, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-23, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-16, 2023-06-23, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-11, 2023-08-17, 2023-08-24, 2023-08-30, 2023-09-07, 2023-09-14, 2023-09-20, 2023-09-28, 2023-10-05, 2023-10-13, 2023-10-20, 2023-10-26, 2023-11-03, 2023-11-09, 2023-11-18, 2023-11-24, 2023-12-01, 2023-12-07, 2023-12-15, 2024-01-04, 2024-01-17, 2024-01-22, 2024-01-25, 2024-02-05, 2024-02-10, 2024-02-17, 2024-02-26, 2024-03-02, 2024-03-11, 2024-03-18, 2024-03-26, 2025-11-27, 2025-11-28</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
@@ -1017,12 +1005,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2024-08-12, 2024-08-13, 2024-10-01, 2024-10-15, 2024-10-21, 2024-11-01, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-07, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-07, 2025-02-17, 2025-03-05, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-08, 2025-04-14, 2025-04-21, 2025-04-28, 2025-05-05, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-14, 2025-06-25, 2025-07-02, 2025-07-07, 2025-07-14, 2025-07-18, 2025-07-31, 2025-08-04, 2025-08-11, 2025-08-25, 2025-09-01, 2025-09-08, 2025-09-15, 2025-09-23, 2025-09-29, 2025-10-06, 2025-10-08, 2025-10-20, 2025-10-27, 2025-11-06, 2025-11-10, 2025-11-19, 2025-11-24, 2025-12-01, 2025-12-10, 2025-12-15, 2025-12-22, 2026-01-14, 2026-01-19, 2026-01-27, 2026-02-02, 2026-02-09, 2026-02-16, 2026-02-25, 2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-25</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2024-08-20, 2024-10-15, 2024-10-17, 2024-11-01, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-07, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-07, 2025-02-17, 2025-03-05, 2025-03-07, 2025-03-10, 2025-03-17, 2025-03-25, 2025-04-03, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-30, 2025-05-05, 2025-05-14, 2025-05-21, 2025-05-26, 2025-06-05, 2025-06-11, 2025-06-20, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-18, 2025-07-21, 2025-07-31, 2025-08-08, 2025-08-12, 2025-08-25, 2025-09-02, 2025-09-08, 2025-09-18, 2025-09-23, 2025-09-29, 2025-10-06, 2025-10-16, 2025-10-21, 2025-10-30, 2025-11-06, 2025-11-10, 2025-11-19, 2025-11-28, 2025-12-03, 2025-12-11, 2025-12-18, 2026-01-14, 2026-01-22, 2026-01-29, 2026-02-04, 2026-02-13, 2026-02-19, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1121,12 +1109,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2024-10-18, 2024-10-21, 2024-10-23, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-20, 2024-11-27, 2024-12-04, 2024-12-11, 2024-12-18, 2025-01-10, 2025-01-16, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-21, 2025-04-28, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-05, 2025-06-12, 2025-06-20, 2025-07-03, 2025-07-10, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-19, 2025-09-26, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25, 2025-12-12, 2025-12-22, 2026-01-14, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26, 2026-03-03, 2026-03-10</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2024-10-21, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-30, 2024-12-07, 2024-12-13, 2024-12-20, 2025-01-10, 2025-01-20, 2025-02-07, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-18, 2025-03-26, 2025-04-01, 2025-04-09, 2025-04-25, 2025-05-06, 2025-05-19, 2025-05-20, 2025-06-05, 2025-06-06, 2025-06-20, 2025-07-03, 2025-07-04, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-25, 2025-09-02, 2025-09-06, 2025-09-15, 2025-09-19, 2025-09-26, 2025-10-08, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-12, 2025-11-19, 2025-11-26, 2025-12-13, 2026-01-08, 2026-01-15, 2026-01-22, 2026-01-29, 2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-04</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1223,12 +1211,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2023-09-13, 2023-09-29, 2023-12-28, 2024-01-06, 2024-01-09, 2024-01-19, 2024-01-27, 2024-02-02, 2024-02-10, 2024-02-14, 2024-02-24, 2024-03-02, 2024-03-11, 2024-03-18, 2024-03-23, 2024-04-06, 2024-04-12, 2024-04-17, 2024-04-29, 2024-05-03, 2024-05-14, 2024-05-21, 2024-05-27, 2024-06-05, 2024-06-12, 2024-06-17, 2024-06-25, 2024-07-03, 2024-07-11, 2024-07-18, 2024-07-24, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-20, 2024-08-23, 2024-09-03, 2024-09-06, 2024-09-18, 2024-09-20, 2024-10-01, 2024-10-09, 2024-10-11, 2024-10-19, 2024-10-26, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-09, 2024-12-14, 2024-12-23, 2024-12-27, 2025-01-08, 2025-01-13, 2025-01-20, 2025-01-24, 2025-01-31, 2025-02-08, 2025-02-14, 2025-02-20, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-22, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-16, 2025-04-26, 2025-05-03, 2025-05-09, 2025-05-17, 2025-05-24, 2025-05-30, 2025-06-06, 2025-06-14, 2025-06-21, 2025-07-01, 2025-07-04, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-16, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-20, 2025-09-27, 2025-10-03, 2025-10-10, 2025-10-16, 2025-10-24, 2025-11-01, 2025-11-08, 2025-11-15, 2025-11-24, 2025-11-29, 2025-12-03, 2025-12-05, 2025-12-18, 2025-12-22, 2025-12-26, 2026-01-06, 2026-01-17, 2026-01-19, 2026-01-24, 2026-01-30, 2026-02-02, 2026-02-03, 2026-02-04, 2026-02-06, 2026-02-09, 2026-02-13, 2026-02-20, 2026-02-26, 2026-03-02, 2026-03-04, 2026-03-05</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-04, 2026-02-06, 2026-02-09, 2026-02-13, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2023-09-29, 2023-12-28, 2024-01-06, 2024-01-12, 2024-01-22, 2024-01-29, 2024-02-05, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-19, 2024-04-06, 2024-04-09, 2024-04-17, 2024-04-22, 2024-04-29, 2024-05-10, 2024-05-14, 2024-05-21, 2024-05-27, 2024-06-05, 2024-06-12, 2024-06-17, 2024-06-25, 2024-07-03, 2024-07-11, 2024-07-18, 2024-07-24, 2024-07-30, 2024-08-08, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-26, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-19, 2024-11-27, 2024-12-06, 2024-12-11, 2024-12-19, 2024-12-27, 2025-01-02, 2025-01-09, 2025-01-16, 2025-01-24, 2025-01-31, 2025-02-03, 2025-02-11, 2025-02-18, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-21, 2025-03-26, 2025-04-03, 2025-04-07, 2025-04-15, 2025-04-23, 2025-05-03, 2025-05-07, 2025-05-13, 2025-05-23, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-17, 2025-06-25, 2025-07-02, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-02, 2025-08-08, 2025-08-16, 2025-08-29, 2025-09-01, 2025-09-12, 2025-09-15, 2025-09-22, 2025-09-30, 2025-10-06, 2025-10-16, 2025-10-24, 2025-10-27, 2025-11-05, 2025-11-11, 2025-11-15, 2025-11-25, 2025-12-01, 2025-12-03, 2025-12-05, 2025-12-16, 2025-12-20, 2025-12-22, 2025-12-26, 2026-01-06, 2026-01-17, 2026-01-19, 2026-01-24, 2026-01-31, 2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-23, 2026-02-28, 2026-03-02, 2026-03-04, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-23, 2026-02-28</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1291,16 +1279,8 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2023-08-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-13, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-11, 2024-03-19, 2024-04-02, 2024-04-11, 2024-04-12, 2024-04-23, 2024-05-03, 2024-05-07, 2024-05-14, 2024-05-22, 2024-05-28, 2024-06-07, 2024-06-12, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-25, 2024-07-29, 2024-07-31, 2024-08-06, 2024-08-15, 2024-08-16, 2024-08-17, 2024-08-25, 2024-08-27, 2024-09-01, 2024-09-05, 2024-09-12, 2024-09-18, 2024-09-26, 2024-10-04, 2024-10-24, 2024-11-01, 2024-11-08, 2024-11-14, 2024-11-15, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-26, 2024-12-27, 2025-01-13, 2025-01-16, 2025-01-17, 2025-01-23, 2025-01-27, 2025-01-30, 2025-02-10, 2025-02-20, 2025-03-10, 2025-03-17, 2025-03-19, 2025-03-31, 2025-04-01, 2025-04-02, 2025-04-10, 2025-04-21, 2025-04-23, 2025-04-24, 2025-04-28, 2025-05-10, 2025-05-19, 2025-05-21, 2025-05-22, 2025-06-18, 2025-06-19, 2025-07-04, 2025-07-07, 2025-07-10, 2025-07-11, 2025-07-14, 2025-07-17, 2025-07-28, 2025-07-31, 2025-08-04, 2025-08-05, 2025-08-08, 2025-08-14, 2025-08-19, 2025-08-29, 2025-09-02, 2025-09-05, 2025-09-08, 2025-09-20, 2025-10-10, 2025-10-24, 2025-11-10, 2025-11-14, 2025-11-27, 2026-03-09</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2023-08-15, 2023-08-22, 2023-08-29, 2023-09-12, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-15, 2024-03-20, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-03, 2024-05-08, 2024-05-16, 2024-05-24, 2024-05-30, 2024-06-07, 2024-06-13, 2024-06-20, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-25, 2024-07-26, 2024-07-29, 2024-08-01, 2024-08-09, 2024-08-16, 2024-08-17, 2024-08-22, 2024-08-25, 2024-08-30, 2024-09-01, 2024-09-06, 2024-09-12, 2024-09-20, 2024-09-27, 2024-10-05, 2024-10-28, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-28, 2024-12-05, 2024-12-26, 2024-12-27, 2025-01-16, 2025-01-17, 2025-01-23, 2025-01-30, 2025-02-07, 2025-02-19, 2025-02-24, 2025-03-11, 2025-03-18, 2025-03-19, 2025-04-01, 2025-04-02, 2025-04-07, 2025-04-10, 2025-04-23, 2025-04-24, 2025-04-30, 2025-05-10, 2025-05-21, 2025-05-22, 2025-06-19, 2025-06-20, 2025-07-04, 2025-07-07, 2025-07-10, 2025-07-11, 2025-07-17, 2025-07-24, 2025-07-29, 2025-08-04, 2025-08-05, 2025-08-06, 2025-08-08, 2025-08-14, 2025-08-19, 2025-08-29, 2025-09-04, 2025-09-05, 2025-09-08, 2025-09-22, 2025-10-10, 2025-10-24, 2025-11-10, 2025-11-14, 2026-03-06, 2026-03-09</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
@@ -1379,12 +1359,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2023-08-14, 2023-08-25, 2025-07-02, 2025-07-08, 2025-07-15, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-04, 2025-12-12, 2026-01-17, 2026-01-22, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-13, 2026-02-25, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-13, 2026-02-25, 2026-02-27</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2023-08-25, 2025-07-08, 2025-07-15, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-04, 2025-12-12, 2026-01-17, 2026-01-22, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1473,12 +1453,12 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2022-12-28, 2023-01-06, 2023-01-10, 2023-01-17, 2023-01-24, 2023-01-31, 2023-02-07, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-19, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-24, 2023-05-30, 2023-06-07, 2023-06-16, 2023-06-22, 2023-06-28, 2023-07-06, 2023-07-13, 2023-07-22, 2023-07-26, 2023-07-31, 2023-08-10, 2023-08-16, 2023-08-25, 2023-09-02, 2023-09-07, 2023-09-13, 2023-09-22, 2023-10-02, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-25, 2023-11-01, 2023-11-09, 2023-11-15, 2023-11-23, 2023-11-30, 2023-12-11, 2024-01-16, 2024-01-25, 2024-02-02, 2024-02-09, 2024-02-14, 2024-02-21, 2024-03-01, 2024-03-08, 2024-03-13, 2024-03-15, 2024-03-22, 2024-04-04, 2024-04-05, 2024-04-11, 2024-04-17, 2024-04-25, 2024-05-03, 2024-05-07, 2024-05-15, 2024-05-23, 2024-05-30, 2024-06-05, 2024-06-06, 2024-06-12, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-12, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-08, 2024-10-18, 2024-10-22, 2024-10-28, 2024-11-05, 2024-11-14, 2024-11-21, 2024-11-29, 2025-01-03, 2025-01-16, 2025-03-11, 2025-03-20, 2025-03-25, 2025-03-28, 2025-04-10, 2025-04-22, 2025-05-01, 2025-05-08, 2025-05-13, 2025-05-22, 2025-05-29, 2025-06-03, 2025-06-12, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-29, 2025-08-05, 2025-08-12, 2025-08-19, 2025-08-26, 2025-09-02, 2025-09-10, 2025-09-16, 2025-09-23, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-07, 2026-01-22, 2026-01-29, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-03</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2023-01-06, 2023-01-13, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-19, 2023-05-26, 2023-05-31, 2023-06-07, 2023-06-16, 2023-06-26, 2023-06-28, 2023-07-07, 2023-07-13, 2023-07-22, 2023-07-26, 2023-08-09, 2023-08-16, 2023-08-18, 2023-08-28, 2023-09-02, 2023-09-07, 2023-09-16, 2023-09-22, 2023-10-02, 2023-10-06, 2023-10-13, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-11, 2023-11-16, 2023-11-24, 2023-11-30, 2023-12-11, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-15, 2024-02-22, 2024-03-01, 2024-03-08, 2024-03-14, 2024-03-22, 2024-04-05, 2024-04-11, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-23, 2024-05-31, 2024-06-06, 2024-06-12, 2024-06-20, 2024-06-28, 2024-07-04, 2024-07-12, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-12, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-09, 2024-10-18, 2024-10-25, 2024-10-30, 2024-11-08, 2024-11-15, 2024-11-21, 2024-11-29, 2025-01-03, 2025-03-11, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-01, 2025-05-08, 2025-05-13, 2025-05-23, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-18, 2025-07-22, 2025-07-31, 2025-08-06, 2025-08-14, 2025-08-19, 2025-08-26, 2025-09-04, 2025-09-12, 2025-09-19, 2025-09-23, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-13, 2026-01-22, 2026-01-29, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-05</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1571,12 +1551,12 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2024-03-20, 2024-03-23, 2024-04-01, 2024-04-06, 2024-04-15, 2024-04-22, 2024-04-27, 2024-05-06, 2024-05-13, 2024-05-18, 2024-05-26, 2024-05-31, 2024-06-07, 2024-06-16, 2024-06-23, 2024-06-27, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-25, 2024-08-02, 2024-08-09, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-05, 2024-10-10, 2024-10-18, 2024-10-26, 2024-11-01, 2024-11-08, 2024-11-16, 2024-11-23, 2024-11-29, 2024-12-06, 2024-12-14, 2024-12-20, 2025-01-17, 2025-01-24, 2025-02-01, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-03, 2025-03-10, 2025-03-21, 2025-03-29, 2025-04-06, 2025-04-13, 2025-04-22, 2025-04-23, 2025-05-02, 2025-05-10, 2025-05-19, 2025-05-26, 2025-05-30, 2025-06-09, 2025-06-14, 2025-06-19, 2025-06-27, 2025-06-28, 2025-07-04, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-01, 2025-08-09, 2025-08-15, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-13, 2025-09-20, 2025-09-27, 2025-10-04, 2025-10-11, 2025-10-17, 2025-10-25, 2025-10-29, 2025-11-07, 2025-11-10, 2025-11-21, 2025-11-22, 2025-11-26, 2025-12-06, 2025-12-13, 2025-12-20, 2025-12-22, 2026-01-08, 2026-01-13, 2026-01-22, 2026-02-26, 2026-03-03, 2026-03-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2024-03-20, 2024-03-23, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-13, 2024-05-18, 2024-05-26, 2024-05-31, 2024-06-07, 2024-06-16, 2024-06-23, 2024-06-27, 2024-07-05, 2024-07-12, 2024-07-21, 2024-07-26, 2024-08-03, 2024-08-09, 2024-08-17, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-26, 2024-10-05, 2024-10-11, 2024-10-18, 2024-10-26, 2024-11-01, 2024-11-08, 2024-11-17, 2024-11-23, 2024-11-29, 2024-12-07, 2024-12-14, 2024-12-20, 2025-01-17, 2025-01-24, 2025-02-01, 2025-02-08, 2025-02-15, 2025-02-22, 2025-02-28, 2025-03-08, 2025-03-14, 2025-03-21, 2025-03-29, 2025-04-06, 2025-04-13, 2025-04-22, 2025-04-23, 2025-05-04, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-02, 2025-06-09, 2025-06-16, 2025-06-19, 2025-06-21, 2025-06-28, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-13, 2025-09-20, 2025-09-27, 2025-10-04, 2025-10-11, 2025-10-18, 2025-10-25, 2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29, 2025-12-06, 2025-12-14, 2025-12-20, 2025-12-22, 2026-01-13, 2026-02-10, 2026-02-28, 2026-03-03, 2026-03-06</t>
+          <t>2026-02-10, 2026-02-28</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1639,16 +1619,8 @@
       <c r="P15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>2024-03-04, 2024-03-09, 2024-03-15, 2024-03-23, 2024-04-01, 2024-04-06, 2024-04-13, 2024-04-20, 2024-04-29, 2024-05-04, 2024-05-11, 2024-05-18, 2024-05-25, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-19, 2024-12-23, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-25, 2025-03-06, 2025-03-14, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-05-02, 2025-05-08, 2025-05-16, 2025-05-22, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-07, 2025-07-10, 2025-07-25, 2025-08-13, 2025-09-04, 2025-10-17, 2025-10-24, 2025-11-13, 2025-11-21</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2024-03-04, 2024-03-09, 2024-03-15, 2024-03-23, 2024-04-01, 2024-04-06, 2024-04-13, 2024-04-22, 2024-04-29, 2024-05-04, 2024-05-11, 2024-05-18, 2024-05-27, 2024-05-31, 2024-06-07, 2024-06-13, 2024-06-26, 2024-06-28, 2024-07-04, 2024-07-18, 2024-07-19, 2024-07-25, 2024-08-05, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-10-31, 2024-11-08, 2024-11-15, 2024-11-21, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-20, 2025-01-10, 2025-01-23, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-22, 2025-02-27, 2025-03-14, 2025-03-20, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-25, 2025-05-02, 2025-05-13, 2025-05-19, 2025-05-23, 2025-06-06, 2025-06-14, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-07, 2025-07-25, 2025-08-13, 2025-10-17, 2025-10-18, 2025-10-24, 2025-11-21</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
@@ -1703,12 +1675,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2023-11-14, 2023-11-16, 2023-11-21, 2023-11-28, 2023-12-07, 2023-12-15, 2024-01-12, 2024-01-18, 2024-01-25, 2024-02-02, 2024-02-10, 2024-02-15, 2024-02-23, 2024-03-08, 2024-03-14, 2024-03-21, 2024-04-01, 2024-04-06, 2024-04-12, 2024-04-20, 2024-04-27, 2024-05-04, 2024-05-11, 2024-05-18, 2024-05-26, 2024-06-01, 2024-06-08, 2024-06-15, 2024-06-21, 2024-07-02, 2024-07-13, 2024-07-21, 2024-07-25, 2024-08-01, 2024-08-09, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-09, 2024-09-13, 2024-09-24, 2024-09-26, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-06, 2024-12-14, 2024-12-27, 2025-01-24, 2025-02-02, 2025-02-08, 2025-02-13, 2025-02-22, 2025-03-01, 2025-03-03, 2025-03-14, 2025-03-17, 2025-03-30, 2025-04-06, 2025-04-13, 2025-04-23, 2025-05-04, 2025-05-11, 2025-05-18, 2025-05-25, 2025-06-01, 2025-06-05, 2025-06-13, 2025-06-21, 2025-06-27, 2025-07-05, 2025-07-12, 2025-07-21, 2025-07-27, 2025-08-09, 2025-08-16, 2025-08-24, 2025-08-29, 2025-09-13, 2025-09-17, 2025-09-18, 2025-09-19, 2025-09-24, 2025-09-29, 2025-10-07, 2025-10-16, 2025-10-17, 2025-10-26, 2025-10-28, 2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29, 2026-02-05, 2026-02-28, 2026-03-02, 2026-03-03, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2023-11-14, 2023-11-17, 2023-11-23, 2023-12-01, 2023-12-07, 2023-12-15, 2024-01-14, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-10, 2024-02-15, 2024-02-23, 2024-03-01, 2024-03-09, 2024-03-15, 2024-03-21, 2024-04-01, 2024-04-06, 2024-04-20, 2024-04-27, 2024-05-05, 2024-05-11, 2024-05-18, 2024-05-26, 2024-06-01, 2024-06-08, 2024-06-15, 2024-06-21, 2024-07-02, 2024-07-13, 2024-07-21, 2024-07-26, 2024-08-03, 2024-08-09, 2024-08-17, 2024-08-26, 2024-08-31, 2024-09-09, 2024-09-14, 2024-09-24, 2024-09-27, 2024-10-05, 2024-10-11, 2024-10-19, 2024-10-25, 2024-11-01, 2024-11-09, 2024-11-16, 2024-11-23, 2024-12-01, 2024-12-07, 2024-12-14, 2025-01-18, 2025-01-25, 2025-02-03, 2025-02-08, 2025-02-15, 2025-02-23, 2025-03-01, 2025-03-09, 2025-03-14, 2025-03-22, 2025-03-30, 2025-04-08, 2025-04-13, 2025-04-26, 2025-05-04, 2025-05-11, 2025-05-18, 2025-05-25, 2025-06-02, 2025-06-08, 2025-06-13, 2025-06-21, 2025-06-27, 2025-07-05, 2025-07-13, 2025-07-21, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-24, 2025-08-30, 2025-09-13, 2025-09-17, 2025-09-18, 2025-09-19, 2025-09-24, 2025-09-29, 2025-10-07, 2025-10-16, 2025-10-17, 2025-10-27, 2025-10-28, 2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29, 2026-02-05, 2026-02-28, 2026-03-02, 2026-03-03, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -1799,12 +1771,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2024-05-29, 2024-06-04, 2024-06-11, 2024-06-26, 2024-07-06, 2024-07-12, 2024-07-17, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2025-01-08, 2025-01-14, 2025-01-21, 2025-01-29, 2025-02-04, 2025-02-11, 2025-02-20, 2025-02-25, 2025-03-05, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-02, 2025-04-09, 2025-04-23, 2025-04-30, 2025-05-08, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-03, 2025-07-09, 2025-07-16, 2025-07-23, 2025-08-01, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-27, 2025-09-03, 2025-09-12, 2025-09-17, 2025-09-24, 2025-10-02, 2025-10-08, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-06, 2025-11-14, 2025-11-19, 2025-11-26, 2025-12-03, 2025-12-10, 2025-12-17, 2026-01-15, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-04, 2026-03-09</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2024-06-04, 2024-06-11, 2024-06-22, 2024-06-27, 2024-07-06, 2024-07-12, 2024-07-18, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-04, 2024-12-12, 2024-12-18, 2025-01-10, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-07, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-07, 2025-03-17, 2025-03-21, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-25, 2025-04-30, 2025-05-09, 2025-05-15, 2025-05-22, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-08-01, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-12, 2025-09-18, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-16, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-28, 2025-12-05, 2025-12-12, 2025-12-19, 2026-01-16, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27, 2026-03-06</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -1901,12 +1873,12 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2025-07-02, 2025-07-18, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-20, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-10-01, 2025-10-09, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-12, 2025-11-20, 2025-11-26, 2025-12-03, 2025-12-10, 2025-12-17, 2026-01-07, 2026-01-14, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-11</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2025-07-18, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-14, 2025-08-20, 2025-09-03, 2025-09-16, 2025-09-18, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-17, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-12, 2025-11-20, 2025-12-01, 2025-12-04, 2025-12-12, 2026-01-07, 2026-01-10, 2026-01-16, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -1995,12 +1967,12 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2022-11-29, 2022-12-16, 2022-12-20, 2022-12-28, 2023-01-13, 2023-01-18, 2023-01-24, 2023-01-31, 2023-02-07, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-29, 2023-04-04, 2023-04-11, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-16, 2023-05-24, 2023-05-30, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-04, 2023-07-11, 2023-07-19, 2023-07-25, 2023-08-01, 2023-08-09, 2023-08-16, 2023-08-22, 2023-08-29, 2023-09-05, 2024-10-16, 2024-11-05, 2025-01-16, 2025-01-23, 2025-01-24, 2025-02-05, 2025-02-10, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-09, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-06, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-06, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-07, 2026-01-22, 2026-01-27, 2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-03</t>
+          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2022-12-12, 2022-12-19, 2022-12-26, 2022-12-29, 2023-01-13, 2023-01-19, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-11, 2023-04-13, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-22, 2023-06-29, 2023-07-05, 2023-07-15, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-10, 2023-08-16, 2023-08-23, 2023-08-31, 2023-09-05, 2024-11-05, 2025-01-16, 2025-01-23, 2025-01-24, 2025-02-10, 2025-02-21, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-09, 2025-05-22, 2025-05-29, 2025-06-07, 2025-06-12, 2025-06-20, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-06, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-13, 2026-01-22, 2026-01-27, 2026-02-04, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2063,16 +2035,8 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>2023-10-23, 2023-11-10, 2023-12-07, 2023-12-15, 2024-02-05, 2024-02-12, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-05, 2024-04-08, 2024-04-23, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-19, 2025-01-07, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-07, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-17, 2025-03-19, 2025-03-25, 2025-04-02, 2025-04-03, 2025-04-23, 2025-04-29, 2025-05-08, 2025-05-13, 2025-05-21, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-18, 2025-06-24, 2025-07-02, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-30, 2025-08-06, 2025-08-14, 2025-08-20, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>2023-11-10, 2023-12-15, 2024-02-05, 2024-02-12, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-08, 2024-04-23, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-28, 2024-06-05, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-04, 2024-07-12, 2024-07-19, 2024-07-25, 2024-08-02, 2024-08-09, 2024-08-15, 2024-08-23, 2024-08-29, 2024-09-05, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-01, 2024-10-09, 2024-10-16, 2024-10-24, 2024-10-29, 2024-11-07, 2024-11-15, 2024-11-21, 2024-11-28, 2024-12-03, 2024-12-12, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-21, 2025-01-30, 2025-02-05, 2025-02-11, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-17, 2025-03-20, 2025-03-27, 2025-04-02, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-30, 2025-08-06, 2025-08-14, 2025-08-20, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="n">
@@ -2127,14 +2091,10 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2022-08-26, 2022-08-31, 2022-09-07, 2022-09-14, 2022-09-21, 2022-09-28, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-09, 2022-11-16, 2022-11-28, 2022-12-05, 2022-12-13, 2022-12-26, 2023-01-03, 2023-01-10, 2023-01-27, 2023-01-30, 2023-02-06, 2023-02-13, 2023-02-21, 2023-02-27, 2023-03-06, 2023-03-13, 2023-03-21, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-20, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-08, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-19, 2023-08-29, 2023-08-30, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-22, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-19, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-13, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-13, 2024-03-19, 2024-04-02, 2024-04-10, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-09, 2024-09-16, 2024-09-24, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-06, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-05, 2024-12-09, 2024-12-16, 2024-12-27, 2025-01-13, 2025-01-20, 2025-01-27, 2025-01-28, 2025-01-29, 2025-02-05, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-04, 2025-03-06, 2025-03-10, 2025-03-17, 2025-03-25, 2025-04-01, 2025-04-07, 2025-04-21, 2025-04-28, 2025-05-06, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-05, 2025-06-10, 2025-06-17, 2025-06-26, 2025-07-01, 2025-07-07, 2025-07-14, 2025-07-21, 2025-07-30, 2025-07-31, 2025-08-04, 2025-08-08, 2025-08-09, 2025-08-13, 2025-08-22, 2025-08-25, 2025-08-27, 2025-09-09, 2025-09-12, 2025-09-17, 2025-09-25, 2025-10-02, 2025-11-19, 2026-02-11</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>2022-08-26, 2022-08-31, 2022-09-07, 2022-09-14, 2022-09-21, 2022-09-28, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-09, 2022-11-16, 2022-11-29, 2022-12-05, 2022-12-13, 2023-01-03, 2023-01-10, 2023-01-27, 2023-01-30, 2023-01-31, 2023-02-07, 2023-02-14, 2023-02-27, 2023-02-28, 2023-03-13, 2023-03-14, 2023-03-21, 2023-03-29, 2023-04-05, 2023-04-11, 2023-04-21, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-24, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-26, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-08, 2024-02-16, 2024-02-22, 2024-03-01, 2024-03-06, 2024-03-13, 2024-03-21, 2024-04-03, 2024-04-11, 2024-04-17, 2024-04-25, 2024-05-03, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-07, 2024-06-12, 2024-06-20, 2024-06-27, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-30, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-25, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-31, 2024-11-08, 2024-11-15, 2024-11-20, 2024-11-28, 2024-12-04, 2024-12-05, 2024-12-11, 2024-12-19, 2025-01-10, 2025-01-17, 2025-01-21, 2025-01-27, 2025-01-28, 2025-01-29, 2025-02-07, 2025-02-12, 2025-02-19, 2025-02-27, 2025-03-04, 2025-03-06, 2025-03-12, 2025-03-19, 2025-03-27, 2025-04-02, 2025-04-09, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-21, 2025-05-28, 2025-06-05, 2025-06-12, 2025-06-18, 2025-06-26, 2025-07-02, 2025-07-10, 2025-07-17, 2025-07-23, 2025-07-30, 2025-07-31, 2025-08-04, 2025-08-08, 2025-08-09, 2025-08-13, 2025-08-22, 2025-08-25, 2025-08-27, 2025-09-09, 2025-09-12, 2025-09-17, 2025-09-25, 2025-10-09, 2025-11-20, 2026-03-06</t>
-        </is>
-      </c>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
@@ -2221,12 +2181,12 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-23, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-07, 2024-03-13, 2024-03-20, 2024-03-27, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-09, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-28, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-16, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-20, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2024-12-23, 2025-01-07, 2025-01-10, 2025-01-13, 2025-01-14, 2025-01-22, 2025-01-29, 2025-02-05, 2025-02-12, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-03, 2025-04-09, 2025-04-16, 2025-04-23, 2025-04-30, 2025-05-02, 2025-05-07, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-16, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-11, 2025-08-26, 2025-08-27, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-10-01, 2025-10-08, 2025-10-15, 2025-10-21, 2025-10-29, 2025-11-04, 2025-11-17, 2025-11-19, 2025-11-26, 2025-12-05, 2025-12-10, 2025-12-22, 2025-12-27, 2025-12-29, 2026-01-07, 2026-01-15, 2026-01-21, 2026-01-28, 2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-14, 2026-02-16, 2026-02-18, 2026-02-20, 2026-02-24, 2026-02-25, 2026-03-04</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-14, 2026-02-16, 2026-02-18, 2026-02-20, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-18, 2023-08-24, 2023-09-02, 2023-09-07, 2023-09-15, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-13, 2023-10-19, 2023-10-27, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-23, 2023-12-01, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-02, 2024-01-05, 2024-01-12, 2024-01-19, 2024-01-25, 2024-02-02, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-20, 2024-03-27, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-30, 2024-05-02, 2024-05-11, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-20, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-19, 2025-01-07, 2025-01-10, 2025-01-13, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-14, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-04, 2025-04-10, 2025-04-23, 2025-04-24, 2025-05-02, 2025-05-07, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-11, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-26, 2025-08-28, 2025-09-10, 2025-09-11, 2025-09-23, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-20, 2025-10-24, 2025-10-30, 2025-11-04, 2025-11-17, 2025-11-20, 2025-12-05, 2025-12-13, 2025-12-22, 2025-12-27, 2026-01-07, 2026-01-13, 2026-01-21, 2026-01-27, 2026-01-30, 2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25, 2026-03-09</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2289,16 +2249,8 @@
       <c r="P23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2022-08-09, 2022-08-18, 2022-08-23, 2022-08-31, 2022-09-06, 2022-09-15, 2022-09-20, 2022-09-28, 2022-10-04, 2022-10-11, 2022-10-18, 2022-10-24, 2022-10-31, 2022-11-08, 2022-11-15, 2022-11-22, 2022-11-28, 2022-12-06, 2022-12-13, 2022-12-19, 2022-12-27, 2023-01-04, 2023-01-10, 2023-01-18, 2023-01-24, 2023-01-30, 2023-02-08, 2023-02-16, 2023-02-22, 2023-03-03, 2023-03-08, 2023-03-13, 2023-03-21, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-15, 2023-05-23, 2023-05-30, 2023-06-05, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-22, 2023-08-28, 2023-09-06, 2023-09-11, 2023-09-18, 2023-09-26, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-22, 2023-10-30, 2023-11-06, 2023-11-14, 2023-11-23, 2023-11-27, 2023-12-05, 2023-12-11, 2023-12-27, 2024-01-09, 2024-01-15, 2024-01-24, 2024-01-29, 2024-02-05, 2024-02-14, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-13, 2024-04-17, 2024-04-23, 2024-04-29, 2024-05-03, 2024-05-04, 2024-05-05, 2024-05-17, 2024-05-21, 2024-05-27, 2024-05-30, 2024-06-12, 2024-06-15, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-15, 2024-07-19, 2024-07-22, 2024-07-25, 2024-07-29, 2024-08-05, 2024-08-09, 2024-08-10, 2024-08-12, 2024-08-14, 2024-08-17, 2024-08-22, 2024-08-24, 2024-08-29, 2024-09-02, 2024-09-06, 2024-09-07, 2024-09-14, 2024-09-20, 2024-09-23, 2024-10-16, 2024-10-24, 2024-10-29, 2024-11-01, 2025-02-24, 2025-03-05</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>2022-08-09, 2022-08-18, 2022-08-23, 2022-09-02, 2022-09-07, 2022-09-19, 2022-09-20, 2022-09-30, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-08, 2022-11-15, 2022-11-23, 2022-11-30, 2022-12-07, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-06, 2023-01-12, 2023-01-19, 2023-01-31, 2023-02-02, 2023-02-13, 2023-02-16, 2023-02-24, 2023-03-07, 2023-03-09, 2023-03-15, 2023-03-23, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-27, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-08, 2023-07-15, 2023-07-21, 2023-08-02, 2023-08-09, 2023-08-18, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-16, 2023-09-20, 2023-09-29, 2023-10-06, 2023-10-17, 2023-10-18, 2023-10-30, 2023-11-01, 2023-11-08, 2023-11-17, 2023-11-27, 2023-11-30, 2023-12-08, 2023-12-14, 2023-12-28, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-09, 2024-02-16, 2024-02-23, 2024-03-01, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-15, 2024-04-18, 2024-04-26, 2024-05-02, 2024-05-04, 2024-05-05, 2024-05-09, 2024-05-17, 2024-05-21, 2024-05-28, 2024-05-30, 2024-06-12, 2024-06-15, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-18, 2024-07-19, 2024-07-22, 2024-07-25, 2024-07-27, 2024-08-01, 2024-08-05, 2024-08-08, 2024-08-09, 2024-08-10, 2024-08-13, 2024-08-14, 2024-08-17, 2024-08-22, 2024-08-28, 2024-08-29, 2024-09-03, 2024-09-06, 2024-09-12, 2024-09-20, 2024-10-02, 2024-10-16, 2024-10-24, 2024-10-29, 2024-11-01, 2025-03-05</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="n">
@@ -2351,16 +2303,8 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>2022-08-03, 2022-08-09, 2022-08-18, 2022-08-23, 2022-08-30, 2022-09-06, 2022-09-15, 2022-09-20, 2022-09-27, 2022-10-04, 2022-10-11, 2022-10-18, 2022-10-24, 2022-10-31, 2022-11-08, 2022-11-15, 2022-11-21, 2022-11-28, 2022-12-05, 2022-12-13, 2022-12-19, 2022-12-27, 2023-01-04, 2023-01-10, 2023-01-16, 2023-01-24, 2023-01-31, 2023-02-08, 2023-02-15, 2023-02-22, 2023-02-28, 2023-03-08, 2023-03-13, 2023-03-21, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-15, 2023-05-23, 2023-05-30, 2023-06-05, 2023-06-14, 2023-06-21, 2023-06-27, 2023-07-05, 2023-07-10, 2023-07-19, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-11, 2023-09-18, 2023-09-25, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-24, 2023-10-30, 2023-11-07, 2023-11-14, 2023-11-24, 2023-12-04, 2023-12-11, 2023-12-18, 2023-12-26, 2024-01-02, 2024-01-09, 2024-01-15, 2024-01-22, 2024-01-29, 2024-02-07, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-04, 2024-04-08, 2024-04-15, 2024-04-23, 2024-04-29, 2024-05-03, 2024-05-05, 2024-05-17, 2024-05-21, 2024-05-27, 2024-05-30, 2024-06-12, 2024-06-13, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-15, 2024-07-22, 2024-07-29, 2024-07-30, 2024-08-05, 2024-08-12, 2024-08-23, 2024-08-30, 2024-09-04, 2024-09-13, 2024-09-25, 2024-10-29, 2025-02-24, 2025-03-05</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>2022-08-05, 2022-08-09, 2022-08-18, 2022-08-23, 2022-09-01, 2022-09-07, 2022-09-19, 2022-09-20, 2022-09-30, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-08, 2022-11-15, 2022-11-23, 2022-11-30, 2022-12-07, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-06, 2023-01-12, 2023-01-18, 2023-01-26, 2023-02-02, 2023-02-13, 2023-02-16, 2023-02-24, 2023-03-03, 2023-03-09, 2023-03-15, 2023-03-23, 2023-03-30, 2023-04-05, 2023-04-12, 2023-04-27, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-25, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-08, 2023-07-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-08, 2023-09-18, 2023-09-25, 2023-10-02, 2023-10-09, 2023-10-16, 2023-10-20, 2023-10-26, 2023-11-02, 2023-11-13, 2023-11-15, 2023-11-29, 2023-12-07, 2023-12-18, 2023-12-20, 2023-12-28, 2024-01-03, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-09, 2024-02-14, 2024-02-22, 2024-03-01, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-13, 2024-04-18, 2024-04-26, 2024-05-02, 2024-05-05, 2024-05-09, 2024-05-17, 2024-05-21, 2024-05-28, 2024-05-30, 2024-06-12, 2024-06-13, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-17, 2024-07-23, 2024-07-29, 2024-07-30, 2024-08-05, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-04, 2024-09-25, 2024-11-01, 2025-02-24, 2025-03-05</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="n">
@@ -2447,12 +2391,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2025-05-28, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-29, 2025-08-06, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-09, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2025-12-23, 2026-01-06, 2026-01-13, 2026-01-20, 2026-01-27, 2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24, 2026-03-03, 2026-03-10</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2025-06-04, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-29, 2025-08-06, 2025-08-12, 2025-08-20, 2025-09-02, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-10, 2025-10-17, 2025-10-23, 2025-10-29, 2025-11-06, 2025-11-14, 2025-11-20, 2025-11-27, 2025-12-05, 2025-12-11, 2025-12-18, 2025-12-26, 2026-01-08, 2026-01-15, 2026-01-22, 2026-01-30, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2541,12 +2485,12 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2022-09-02, 2022-09-06, 2022-09-13, 2022-09-20, 2022-09-27, 2022-10-11, 2022-10-18, 2022-10-25, 2022-11-01, 2022-11-08, 2022-11-15, 2022-11-21, 2022-11-28, 2022-12-05, 2022-12-12, 2022-12-19, 2022-12-26, 2023-01-02, 2023-01-10, 2023-01-16, 2023-01-23, 2023-01-30, 2023-02-06, 2023-02-13, 2023-02-22, 2023-02-23, 2023-03-07, 2023-03-15, 2023-03-23, 2023-03-29, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-01, 2024-02-14, 2024-02-20, 2024-02-28, 2024-03-05, 2024-03-13, 2024-03-19, 2024-04-02, 2024-04-10, 2024-04-16, 2024-04-23, 2024-05-02, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-14, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-25, 2024-10-02, 2024-10-10, 2024-10-16, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2024-12-23, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-13, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-29, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-02, 2025-07-08, 2025-07-17, 2025-07-22, 2025-07-29, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-28, 2025-09-02, 2025-09-09, 2025-09-24, 2025-09-30, 2025-10-06, 2025-10-07, 2025-10-14, 2025-10-17, 2025-10-21, 2025-10-22, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-21, 2025-11-25, 2025-11-28, 2025-12-01, 2025-12-03, 2025-12-05, 2025-12-09, 2025-12-15, 2025-12-22, 2026-01-02, 2026-01-07, 2026-01-13, 2026-01-17, 2026-01-23, 2026-01-24, 2026-01-30, 2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2022-09-08, 2022-09-15, 2022-09-21, 2022-09-28, 2022-10-12, 2022-10-19, 2022-10-29, 2022-11-02, 2022-11-09, 2022-11-16, 2022-11-25, 2022-11-30, 2022-12-09, 2022-12-14, 2022-12-26, 2022-12-27, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-26, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-31, 2023-06-01, 2023-06-09, 2023-06-15, 2023-06-23, 2023-06-29, 2023-07-07, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-26, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-07, 2023-12-13, 2023-12-21, 2023-12-27, 2024-01-03, 2024-01-12, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-29, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-04, 2024-04-10, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-06, 2024-06-12, 2024-06-18, 2024-06-27, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-21, 2024-08-29, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-21, 2024-11-27, 2024-12-04, 2024-12-12, 2024-12-18, 2025-01-08, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-12, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-14, 2025-03-20, 2025-03-26, 2025-04-03, 2025-04-09, 2025-04-16, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-06, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-09, 2025-07-18, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-15, 2025-08-21, 2025-08-30, 2025-09-04, 2025-09-16, 2025-09-25, 2025-10-02, 2025-10-06, 2025-10-10, 2025-10-17, 2025-10-21, 2025-10-22, 2025-10-24, 2025-10-30, 2025-11-07, 2025-11-11, 2025-11-13, 2025-11-18, 2025-11-21, 2025-11-26, 2025-11-28, 2025-12-03, 2025-12-05, 2025-12-11, 2025-12-19, 2025-12-22, 2026-01-02, 2026-01-07, 2026-01-13, 2026-01-17, 2026-01-23, 2026-01-24, 2026-01-30, 2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26, 2026-03-04, 2026-03-06</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -2611,12 +2555,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2022-11-22, 2022-11-30, 2022-12-06, 2022-12-13, 2022-12-20, 2022-12-28, 2023-01-03, 2023-01-10, 2023-01-17, 2023-01-24, 2023-01-31, 2023-02-08, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-18, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-05, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-19, 2023-12-26, 2024-01-02, 2024-01-09, 2024-01-12, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-13, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-12, 2024-03-19, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-12, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-27, 2024-12-03, 2024-12-10, 2025-01-09, 2025-09-26, 2025-10-08, 2025-10-14, 2025-10-28, 2025-10-31, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2026-01-13, 2026-01-30, 2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27, 2026-03-03, 2026-03-10</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2022-11-26, 2022-11-30, 2022-12-09, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-04, 2023-01-12, 2023-01-18, 2023-01-25, 2023-02-03, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-08, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-12, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-15, 2024-02-22, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-09, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-20, 2024-06-26, 2024-07-04, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-29, 2024-09-04, 2024-09-13, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-24, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-20, 2024-11-27, 2024-12-04, 2024-12-11, 2025-01-09, 2025-09-26, 2025-10-08, 2025-10-14, 2025-10-29, 2025-11-04, 2025-11-11, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2026-01-13, 2026-01-30, 2026-02-03, 2026-02-24, 2026-02-27, 2026-03-03, 2026-03-10</t>
+          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -2701,12 +2645,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2023-08-14, 2023-08-15, 2023-08-25, 2023-08-27, 2023-08-30, 2023-09-06, 2023-10-05, 2023-10-19, 2023-10-26, 2023-11-03, 2023-11-09, 2023-11-17, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-04, 2024-01-12, 2024-01-18, 2024-01-25, 2024-02-02, 2024-02-09, 2024-02-15, 2024-02-22, 2024-03-02, 2024-03-08, 2024-03-15, 2024-03-26, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-03, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2024-12-23, 2024-12-30, 2025-01-07, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-22, 2025-04-30, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-13, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-30, 2025-08-06, 2025-08-14, 2025-08-20, 2025-08-27, 2025-09-02, 2025-09-09, 2025-09-17, 2025-09-24, 2025-09-29, 2025-10-02, 2025-10-07, 2025-10-14, 2025-10-15, 2025-10-17, 2025-10-21, 2025-10-24, 2025-10-27, 2025-10-28, 2025-11-05, 2025-11-07, 2025-11-11, 2025-11-12, 2025-11-19, 2025-11-25, 2025-11-28, 2025-12-03, 2025-12-10, 2025-12-27, 2026-01-06, 2026-01-26, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2023-08-14, 2023-08-25, 2023-08-28, 2023-08-30, 2023-09-06, 2023-10-13, 2023-10-20, 2023-10-31, 2023-11-03, 2023-11-10, 2023-11-17, 2023-11-25, 2023-11-30, 2023-12-07, 2023-12-15, 2023-12-21, 2024-01-04, 2024-01-13, 2024-01-19, 2024-01-26, 2024-02-03, 2024-02-15, 2024-02-19, 2024-02-24, 2024-03-02, 2024-03-08, 2024-03-15, 2024-03-27, 2024-04-03, 2024-04-10, 2024-04-22, 2024-04-24, 2024-05-02, 2024-05-14, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-12, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-18, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-09, 2024-12-12, 2024-12-19, 2024-12-26, 2025-01-02, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-21, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-05, 2025-05-08, 2025-05-16, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-08-01, 2025-08-08, 2025-08-14, 2025-08-27, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-15, 2025-10-17, 2025-10-24, 2025-10-27, 2025-10-31, 2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-20, 2025-11-27, 2025-11-28, 2025-12-03, 2025-12-04, 2025-12-12, 2025-12-27, 2026-01-09, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-03-05</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -2769,16 +2713,8 @@
       <c r="P29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>2022-11-23, 2022-11-30, 2022-12-07, 2022-12-14, 2022-12-21, 2022-12-29, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-04, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-10, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-03-27, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-02, 2024-07-08, 2024-07-15, 2024-07-22, 2024-07-29, 2024-08-05, 2024-08-12, 2024-08-20, 2024-08-26, 2024-09-02, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-05, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-07, 2025-01-14, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-14, 2025-04-21, 2025-04-28, 2025-05-05, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-16, 2025-06-24, 2025-07-01, 2025-07-07, 2025-07-14, 2025-07-21, 2025-07-28, 2025-08-04, 2025-08-12, 2025-08-19, 2025-08-25, 2025-09-01, 2025-09-08, 2025-09-15, 2025-09-23, 2025-09-29, 2025-10-08, 2025-10-21, 2025-10-29, 2025-11-04, 2025-11-10, 2025-11-18, 2025-11-24, 2025-12-09, 2025-12-18, 2025-12-23, 2025-12-29, 2026-01-07, 2026-01-14</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>2022-11-24, 2022-12-01, 2022-12-09, 2022-12-15, 2022-12-22, 2022-12-29, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-02, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-03, 2023-03-10, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-05, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-10, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-03, 2024-01-04, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-02, 2024-07-08, 2024-07-15, 2024-07-22, 2024-07-29, 2024-08-12, 2024-08-20, 2024-08-26, 2024-09-02, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-05, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-17, 2025-01-07, 2025-01-14, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-14, 2025-04-21, 2025-04-28, 2025-05-05, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-16, 2025-06-24, 2025-07-01, 2025-07-07, 2025-07-15, 2025-07-21, 2025-07-28, 2025-08-06, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-03, 2025-09-08, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-08, 2025-10-21, 2025-10-29, 2025-11-04, 2025-11-12, 2025-11-18, 2025-11-24, 2025-12-09, 2025-12-18, 2025-12-23, 2025-12-29, 2026-01-07, 2026-01-14</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="n">
@@ -2865,12 +2801,12 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2022-12-22, 2022-12-29, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-03, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-17, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-14, 2023-08-22, 2023-08-28, 2023-09-05, 2023-09-11, 2023-09-19, 2023-09-26, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-24, 2023-10-30, 2023-11-08, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-11, 2023-12-19, 2023-12-27, 2024-01-03, 2024-01-09, 2024-01-15, 2024-01-22, 2024-01-29, 2024-02-05, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-03, 2024-07-08, 2024-07-10, 2024-07-22, 2024-07-29, 2024-08-05, 2024-08-12, 2024-08-20, 2024-08-27, 2024-09-02, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-08, 2024-12-03, 2024-12-10, 2025-01-03, 2025-01-17, 2025-03-13, 2025-05-29, 2025-06-19, 2025-07-07, 2025-07-14, 2025-07-23, 2025-07-31, 2025-08-06, 2025-08-12, 2025-08-29, 2025-09-11, 2025-09-16, 2025-09-22, 2025-10-04, 2025-10-09, 2025-10-15, 2025-10-23, 2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24, 2025-12-02, 2025-12-04, 2025-12-10, 2025-12-17, 2026-01-14, 2026-01-19, 2026-01-20, 2026-01-26, 2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24, 2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2022-12-26, 2022-12-29, 2023-01-06, 2023-01-13, 2023-01-20, 2023-01-27, 2023-02-03, 2023-02-10, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-10, 2023-06-16, 2023-06-23, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-18, 2023-07-25, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-20, 2023-09-26, 2023-10-03, 2023-10-13, 2023-10-17, 2023-10-25, 2023-10-31, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-12, 2023-12-19, 2023-12-27, 2024-01-05, 2024-01-10, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-14, 2024-02-22, 2024-03-01, 2024-03-07, 2024-03-12, 2024-03-19, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-28, 2024-06-05, 2024-06-12, 2024-06-18, 2024-06-25, 2024-07-03, 2024-07-10, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-14, 2024-08-23, 2024-08-29, 2024-09-03, 2024-09-11, 2024-09-17, 2024-09-24, 2024-10-02, 2024-10-09, 2024-10-17, 2024-10-25, 2024-10-30, 2024-11-26, 2024-12-03, 2024-12-10, 2025-01-03, 2025-01-17, 2025-03-14, 2025-05-30, 2025-07-07, 2025-07-14, 2025-07-28, 2025-07-31, 2025-08-06, 2025-08-15, 2025-09-05, 2025-09-11, 2025-09-16, 2025-09-23, 2025-10-04, 2025-10-09, 2025-10-15, 2025-10-23, 2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24, 2025-12-02, 2025-12-04, 2025-12-10, 2025-12-17, 2026-01-14, 2026-01-19, 2026-01-20, 2026-01-26, 2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24, 2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -2933,16 +2869,8 @@
       <c r="P31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>2022-11-17, 2022-12-01, 2022-12-15, 2023-02-03, 2023-02-10, 2023-02-16, 2023-02-23, 2023-03-01, 2023-03-07, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-23, 2023-06-29, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-17, 2023-08-25, 2023-08-31, 2023-09-08, 2023-09-15, 2023-09-21, 2023-09-28, 2023-10-06, 2023-10-13, 2023-10-20, 2023-10-27, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-07, 2024-12-23</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>2022-11-24, 2022-12-01, 2023-02-02, 2023-02-03, 2023-02-13, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-11, 2023-03-17, 2023-03-25, 2023-03-31, 2023-04-14, 2023-04-27, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-09, 2023-06-16, 2023-06-26, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-08-02, 2023-08-05, 2023-08-11, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-15, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-25, 2023-10-27, 2023-11-17, 2023-11-24, 2023-12-06, 2024-02-02</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="n">
@@ -3029,12 +2957,12 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2023-03-14, 2023-03-21, 2023-03-28, 2023-04-03, 2023-04-10, 2023-04-24, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-05, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-09, 2023-08-14, 2023-08-22, 2023-08-28, 2023-09-04, 2023-09-11, 2023-09-18, 2023-09-25, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-23, 2023-10-30, 2023-11-07, 2023-11-14, 2023-11-20, 2023-11-27, 2023-12-04, 2023-12-11, 2023-12-18, 2024-01-09, 2024-01-15, 2024-01-22, 2024-01-29, 2024-02-05, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-07, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-02, 2024-07-08, 2024-07-15, 2024-07-22, 2024-07-29, 2024-08-05, 2024-08-12, 2024-08-20, 2024-08-23, 2024-09-02, 2024-09-10, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-08, 2024-10-15, 2024-10-21, 2024-10-25, 2024-11-05, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-10, 2024-12-17, 2024-12-27, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-23, 2025-04-29, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-28, 2025-06-03, 2025-06-10, 2025-06-18, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-23, 2025-07-29, 2025-08-05, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-09, 2025-09-16, 2025-09-23, 2025-10-01, 2025-10-09, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-12, 2025-11-20, 2025-11-26, 2025-12-03, 2025-12-09, 2025-12-18, 2026-01-14, 2026-01-20, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-03</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-13, 2023-04-26, 2023-05-04, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-26, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-09, 2024-04-17, 2024-04-24, 2024-04-30, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-06, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-05, 2024-09-12, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-27, 2024-12-05, 2024-12-12, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-15, 2026-01-21, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3099,12 +3027,12 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2022-12-07, 2022-12-15, 2022-12-22, 2022-12-29, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-02, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-11, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-18, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-04, 2023-11-15, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2023-12-28, 2024-01-04, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-05, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-10, 2024-03-17, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-03, 2024-05-08, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-15, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-26, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-26, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-31, 2024-11-05, 2024-11-11, 2024-11-16, 2024-11-28, 2024-12-03, 2024-12-10, 2025-01-09, 2025-01-14, 2025-01-21, 2025-01-30, 2025-02-07, 2025-02-14, 2025-02-22, 2025-03-01, 2025-03-18, 2025-04-12, 2025-04-24, 2025-06-19, 2025-12-26, 2025-12-30, 2026-01-02, 2026-01-05, 2026-01-09, 2026-01-13, 2026-01-20, 2026-01-21, 2026-01-22, 2026-01-26, 2026-01-27, 2026-01-28, 2026-01-31, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16, 2026-02-17, 2026-03-02, 2026-03-03</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16, 2026-02-17</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2022-12-09, 2022-12-16, 2022-12-22, 2022-12-30, 2023-01-06, 2023-01-13, 2023-01-20, 2023-01-27, 2023-02-03, 2023-02-10, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-29, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-10, 2023-06-20, 2023-06-26, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-18, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-16, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-20, 2023-10-27, 2023-11-03, 2023-11-10, 2023-11-17, 2023-11-24, 2023-12-01, 2023-12-07, 2023-12-16, 2023-12-21, 2023-12-28, 2024-01-05, 2024-01-13, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-17, 2024-02-23, 2024-03-03, 2024-03-08, 2024-03-16, 2024-04-04, 2024-04-05, 2024-04-12, 2024-04-19, 2024-04-27, 2024-05-03, 2024-05-11, 2024-05-18, 2024-05-24, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-23, 2024-06-27, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-01, 2024-08-10, 2024-08-15, 2024-08-24, 2024-08-26, 2024-08-30, 2024-09-05, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-05, 2024-10-09, 2024-10-18, 2024-10-25, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-21, 2024-11-30, 2024-12-07, 2024-12-13, 2025-01-10, 2025-01-20, 2025-01-25, 2025-02-01, 2025-02-07, 2025-02-14, 2025-02-24, 2025-03-01, 2025-03-26, 2025-04-24, 2025-06-04, 2025-07-04, 2025-12-26, 2025-12-29, 2025-12-30, 2026-01-02, 2026-01-05, 2026-01-09, 2026-01-19, 2026-01-20, 2026-01-21, 2026-01-26, 2026-01-27, 2026-01-28, 2026-01-30, 2026-01-31, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16, 2026-03-02, 2026-03-03</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -3193,12 +3121,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2023-08-14, 2023-08-25, 2023-08-27, 2024-02-14, 2024-02-21, 2024-02-29, 2024-03-07, 2024-03-12, 2024-03-21, 2024-03-27, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-17, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-22, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-05, 2024-12-10, 2024-12-17, 2024-12-27, 2025-01-15, 2025-01-21, 2025-01-28, 2025-02-06, 2025-02-11, 2025-02-18, 2025-02-26, 2025-03-05, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-22, 2025-04-29, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-28, 2025-08-05, 2025-08-12, 2025-08-19, 2025-08-26, 2025-09-02, 2025-09-04, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2025-12-23, 2025-12-30, 2026-01-06, 2026-01-13, 2026-01-20, 2026-01-27, 2026-02-03, 2026-02-10, 2026-02-17, 2026-02-19, 2026-02-24, 2026-03-03, 2026-03-05</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2023-08-25, 2024-01-31, 2024-02-16, 2024-02-24, 2024-03-01, 2024-03-09, 2024-03-16, 2024-03-23, 2024-03-27, 2024-04-04, 2024-04-13, 2024-04-20, 2024-04-27, 2024-05-04, 2024-05-10, 2024-05-18, 2024-05-25, 2024-06-01, 2024-06-07, 2024-06-14, 2024-06-22, 2024-06-29, 2024-07-06, 2024-07-12, 2024-07-19, 2024-07-27, 2024-08-06, 2024-08-10, 2024-08-16, 2024-08-25, 2024-08-31, 2024-09-07, 2024-09-14, 2024-09-21, 2024-09-25, 2024-10-04, 2024-10-12, 2024-10-18, 2024-10-25, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-27, 2024-12-07, 2024-12-12, 2024-12-18, 2025-01-09, 2025-01-17, 2025-01-22, 2025-01-29, 2025-02-08, 2025-02-13, 2025-02-21, 2025-02-27, 2025-03-07, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-03, 2025-04-11, 2025-04-24, 2025-04-30, 2025-05-07, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-06, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-02, 2025-07-11, 2025-07-17, 2025-07-23, 2025-07-31, 2025-08-06, 2025-08-15, 2025-08-21, 2025-08-29, 2025-09-03, 2025-09-11, 2025-09-19, 2025-09-24, 2025-10-01, 2025-10-09, 2025-10-15, 2025-10-25, 2025-10-31, 2025-11-06, 2025-11-11, 2025-11-21, 2025-11-28, 2025-12-04, 2025-12-12, 2025-12-17, 2025-12-27, 2026-01-03, 2026-01-09, 2026-01-16, 2026-01-26, 2026-01-29, 2026-02-07, 2026-02-12, 2026-02-19, 2026-02-24, 2026-03-04, 2026-03-05</t>
+          <t>2026-02-07, 2026-02-12, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3291,12 +3219,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2023-08-14, 2025-12-22, 2025-12-26, 2026-01-02, 2026-01-07, 2026-01-14, 2026-01-22, 2026-01-29, 2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25, 2026-03-04</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2025-12-26, 2026-01-02, 2026-01-08, 2026-01-16, 2026-01-22, 2026-01-30, 2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -3361,12 +3289,12 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2025-10-31, 2025-11-04, 2025-11-06, 2025-11-12, 2025-12-04, 2025-12-17, 2026-01-09, 2026-01-10, 2026-01-13, 2026-01-26, 2026-01-27, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-03-04, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-06, 2025-11-12, 2025-12-04, 2025-12-17, 2025-12-27, 2026-01-09, 2026-01-10, 2026-01-13, 2026-01-27, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-03-04, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -3457,12 +3385,12 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2023-06-07, 2023-06-14, 2023-06-21, 2023-06-29, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-27, 2023-08-03, 2023-08-09, 2023-08-16, 2023-08-24, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-26, 2023-10-05, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-16, 2023-11-22, 2023-11-29, 2023-12-07, 2023-12-13, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-02-01, 2024-02-07, 2024-02-15, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-10, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-30, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-03, 2024-09-11, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-28, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-27, 2024-12-04, 2024-12-12, 2024-12-20, 2025-01-08, 2025-01-15, 2025-01-22, 2025-01-30, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-05, 2025-03-11, 2025-03-20, 2025-03-27, 2025-04-02, 2025-04-09, 2025-04-24, 2025-04-30, 2025-05-07, 2025-05-14, 2025-05-22, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-16, 2025-07-23, 2025-07-31, 2025-08-08, 2025-08-13, 2025-08-20, 2025-08-28, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-25, 2025-10-02, 2025-10-22, 2025-11-01, 2025-11-12, 2025-11-19, 2025-11-27, 2025-12-04, 2025-12-10, 2025-12-18, 2026-01-14, 2026-01-22, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-28, 2023-08-03, 2023-08-10, 2023-08-18, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-06, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-17, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-28, 2024-01-04, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-02, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-20, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-12, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-25, 2025-05-03, 2025-05-08, 2025-05-15, 2025-05-24, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-04, 2025-07-10, 2025-07-18, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-10-02, 2025-10-22, 2025-11-01, 2025-11-12, 2025-11-13, 2025-11-21, 2025-11-27, 2025-12-04, 2025-12-12, 2025-12-18, 2026-01-15, 2026-01-22, 2026-01-30, 2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-05</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -3525,16 +3453,8 @@
       <c r="P38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-19, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-09-01, 2023-09-07, 2023-09-14, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-21, 2023-10-28, 2023-11-03, 2023-11-10, 2023-11-17, 2024-08-06, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-23, 2024-12-27, 2025-01-10, 2025-01-17, 2025-02-07, 2025-02-14, 2025-02-28, 2025-03-07, 2025-03-17, 2025-03-21, 2025-04-09, 2025-05-17</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-09, 2023-06-16, 2023-06-23, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-18, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-15, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-21, 2023-10-28, 2023-11-03, 2023-11-14, 2023-11-17, 2024-08-16, 2024-08-30, 2024-09-06, 2024-09-09, 2024-09-20, 2024-09-25, 2024-10-03, 2024-10-08, 2024-10-17, 2024-10-25, 2024-10-29, 2024-11-06, 2024-11-13, 2024-12-04, 2024-12-09, 2024-12-18, 2024-12-26, 2025-01-09, 2025-01-16, 2025-01-23, 2025-02-12, 2025-02-17, 2025-03-05, 2025-03-12, 2025-03-20, 2025-03-27, 2025-04-11</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="n">
@@ -3621,12 +3541,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2024-06-12, 2024-06-19, 2024-06-24, 2024-07-04, 2024-07-11, 2024-07-17, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-04, 2024-09-12, 2024-09-18, 2024-09-25, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-23, 2024-10-30, 2024-11-06, 2024-11-15, 2024-11-20, 2024-11-28, 2024-12-05, 2024-12-11, 2024-12-19, 2024-12-26, 2025-01-08, 2025-01-16, 2025-01-22, 2025-01-29, 2025-02-03, 2025-02-12, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-02, 2025-04-09, 2025-04-23, 2025-04-30, 2025-05-07, 2025-05-14, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-16, 2025-07-23, 2025-07-31, 2025-08-06, 2025-08-13, 2025-08-21, 2025-09-03, 2025-09-11, 2025-09-18, 2025-09-24, 2025-10-06, 2025-10-09, 2025-10-17, 2025-10-27, 2025-10-30, 2025-11-06, 2025-11-14, 2025-11-20, 2025-11-26, 2025-12-05, 2025-12-11, 2026-01-16, 2026-01-22, 2026-01-28, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2024-06-12, 2024-06-21, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-17, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-19, 2024-12-26, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-19, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-06, 2025-10-09, 2025-10-17, 2025-10-29, 2025-10-30, 2025-11-06, 2025-11-14, 2025-11-21, 2025-11-27, 2025-12-05, 2025-12-11, 2026-01-16, 2026-01-22, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -3723,12 +3643,12 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2024-12-12, 2024-12-21, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-22, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-16, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-20, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-15, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-29, 2025-12-05, 2025-12-11, 2025-12-19, 2026-01-17, 2026-01-22, 2026-01-29, 2026-02-05, 2026-02-14, 2026-02-20, 2026-02-24, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-24</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2025-01-07, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-31, 2025-02-07, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-08, 2025-03-14, 2025-03-22, 2025-03-27, 2025-04-05, 2025-04-12, 2025-04-26, 2025-05-03, 2025-05-10, 2025-05-17, 2025-05-24, 2025-05-31, 2025-06-06, 2025-06-13, 2025-06-21, 2025-06-27, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-25, 2025-08-02, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-24, 2025-11-29, 2025-12-06, 2025-12-12, 2026-01-17, 2026-01-23, 2026-01-31, 2026-02-06, 2026-02-14, 2026-02-21, 2026-02-28, 2026-03-06</t>
+          <t>2026-02-06, 2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -3817,12 +3737,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2023-08-14, 2024-08-20, 2025-01-15, 2025-01-22, 2025-01-29, 2025-02-05, 2025-02-12, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-13, 2025-03-19, 2025-03-26, 2025-04-02, 2025-04-09, 2025-04-16, 2025-04-24, 2025-05-07, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-15, 2025-07-23, 2025-07-25, 2025-08-02, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-27, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-24, 2025-10-28, 2025-10-29, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-26, 2025-12-05, 2025-12-12, 2026-01-09, 2026-01-20, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2024-02-22, 2025-01-15, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-19, 2025-03-26, 2025-04-03, 2025-04-09, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-14, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-02, 2025-08-06, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-05, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-24, 2025-10-29, 2025-11-05, 2025-11-13, 2025-11-19, 2025-11-27, 2025-12-05, 2025-12-12, 2026-01-09, 2026-01-22, 2026-01-30, 2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27, 2026-03-06</t>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -3967,16 +3887,8 @@
       <c r="P43" t="n">
         <v>4</v>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="n">
@@ -4063,12 +3975,12 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2023-09-07, 2023-09-12, 2023-09-19, 2023-09-25, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-19, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-14, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-12, 2024-03-20, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-25, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-18, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-20, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2025-01-16, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-19, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-18, 2025-07-24, 2025-07-31, 2025-08-07, 2025-08-14, 2025-08-21, 2025-08-29, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2025-12-27, 2026-01-14, 2026-01-22, 2026-01-29, 2026-02-03, 2026-02-04, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05, 2026-03-12</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2023-09-07, 2023-09-12, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-23, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-15, 2024-02-21, 2024-02-29, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-21, 2024-07-25, 2024-07-31, 2024-08-08, 2024-08-15, 2024-08-21, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-25, 2024-10-02, 2024-10-11, 2024-10-16, 2024-10-23, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-20, 2024-11-28, 2024-12-04, 2024-12-11, 2025-01-10, 2025-01-16, 2025-01-22, 2025-01-29, 2025-02-05, 2025-02-12, 2025-02-19, 2025-02-28, 2025-03-07, 2025-03-20, 2025-03-21, 2025-03-28, 2025-04-05, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-15, 2025-05-23, 2025-05-30, 2025-06-07, 2025-06-13, 2025-06-26, 2025-06-27, 2025-07-04, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-22, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-24, 2025-11-28, 2025-12-05, 2025-12-12, 2025-12-19, 2025-12-27, 2026-01-14, 2026-01-24, 2026-02-02, 2026-02-03, 2026-02-09, 2026-02-18, 2026-02-21, 2026-03-03, 2026-03-06, 2026-03-16</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-18, 2026-02-21</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -4161,12 +4073,12 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2023-08-04, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-06, 2024-12-13, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-04, 2025-04-10, 2025-04-25, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-13, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-15, 2026-01-22, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-18, 2026-02-26, 2026-03-05, 2026-03-12, 2026-03-19</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2023-08-31, 2024-10-25, 2024-11-02, 2024-11-08, 2024-11-14, 2024-11-21, 2024-11-30, 2024-12-06, 2024-12-13, 2024-12-19, 2025-01-10, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-03-06, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-27, 2025-04-04, 2025-04-12, 2025-04-26, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-31, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-08-01, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-07, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-15, 2026-01-24, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26, 2026-03-05, 2026-03-12</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -4259,12 +4171,12 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2023-08-01, 2023-08-29, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-05, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-22, 2025-04-29, 2025-05-08, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-30, 2025-08-05, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-09, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-22, 2025-10-29, 2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25, 2025-12-02, 2026-01-19, 2026-01-20, 2026-01-27, 2026-02-03, 2026-02-11, 2026-02-18, 2026-02-24, 2026-03-03, 2026-03-10, 2026-03-17</t>
+          <t>2026-02-03, 2026-02-11, 2026-02-18, 2026-02-24</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2025-02-05, 2025-02-11, 2025-02-19, 2025-02-27, 2025-03-05, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-02, 2025-04-10, 2025-04-24, 2025-05-07, 2025-05-08, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-19, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-16, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-27, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-10-01, 2025-10-08, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-18, 2025-11-19, 2025-11-26, 2026-01-13, 2026-01-19, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-21, 2026-02-25, 2026-03-04, 2026-03-11, 2026-03-18</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-21, 2026-02-25</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -4353,12 +4265,12 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2023-02-02, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-19, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-13, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-24, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-29, 2024-12-05, 2024-12-12, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-14, 2025-02-21, 2025-02-27, 2025-03-06, 2025-03-14, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-09, 2025-05-15, 2025-05-23, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-11, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-07, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-07, 2025-11-13, 2025-11-20, 2025-11-28, 2025-12-04, 2025-12-12, 2025-12-20, 2026-01-15, 2026-01-22, 2026-02-21, 2026-02-26, 2026-03-06, 2026-03-14</t>
+          <t>2026-02-21, 2026-02-26</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2023-02-02, 2023-02-10, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-09, 2023-06-16, 2023-06-23, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-18, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-15, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-20, 2023-10-27, 2023-11-03, 2023-11-10, 2023-11-17, 2023-11-24, 2023-12-01, 2023-12-07, 2023-12-15, 2024-01-18, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-23, 2024-03-01, 2024-03-08, 2024-03-15, 2024-03-22, 2024-04-05, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-07, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-20, 2025-01-10, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-15, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-23, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-28, 2025-12-05, 2025-12-12, 2025-12-20, 2026-01-16, 2026-02-13, 2026-02-21, 2026-02-27, 2026-03-06, 2026-03-14</t>
+          <t>2026-02-13, 2026-02-21, 2026-02-27</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -4443,12 +4355,12 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2022-11-30, 2022-12-07, 2022-12-13, 2022-12-21, 2022-12-30, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-21, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-27, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-04, 2023-09-13, 2023-09-21, 2023-09-27, 2023-10-04, 2023-10-10, 2023-10-18, 2023-10-25, 2023-10-31, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-10, 2024-01-25, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-20, 2024-02-28, 2024-03-06, 2024-03-12, 2024-03-19, 2024-04-03, 2024-04-09, 2024-04-16, 2024-04-23, 2024-05-02, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-19, 2024-06-26, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-24, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-08-30, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-21, 2024-10-29, 2024-11-05, 2024-11-13, 2024-11-19, 2024-11-26, 2024-12-02, 2024-12-10, 2024-12-17, 2025-01-07, 2025-01-15, 2025-01-22, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-05, 2025-03-10, 2025-03-18, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-21, 2025-04-28, 2025-05-07, 2025-05-13, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-13, 2025-06-18, 2025-06-25, 2025-07-01, 2025-07-09, 2025-07-15, 2025-07-22, 2025-07-30, 2025-08-05, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-08, 2025-09-16, 2025-09-25, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-22, 2025-10-28, 2025-11-04, 2025-11-12, 2025-11-19, 2025-12-03, 2025-12-17, 2026-01-22, 2026-01-27, 2026-02-04, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-06, 2026-03-10, 2026-03-11, 2026-03-18</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2022-12-02, 2022-12-07, 2022-12-14, 2022-12-22, 2022-12-30, 2023-01-11, 2023-01-20, 2023-01-25, 2023-02-02, 2023-02-08, 2023-02-17, 2023-02-22, 2023-03-01, 2023-03-09, 2023-03-16, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-12, 2023-05-17, 2023-05-25, 2023-05-31, 2023-06-08, 2023-06-14, 2023-06-22, 2023-06-29, 2023-07-05, 2023-07-13, 2023-07-19, 2023-07-26, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-09-01, 2023-09-07, 2023-09-14, 2023-09-22, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-18, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-28, 2024-01-12, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-11, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-04, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-13, 2024-08-21, 2024-08-28, 2024-09-03, 2024-09-05, 2024-09-11, 2024-09-18, 2024-09-24, 2024-10-08, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-31, 2024-11-06, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-04, 2024-12-12, 2024-12-18, 2025-01-08, 2025-01-16, 2025-01-22, 2025-01-28, 2025-02-06, 2025-02-13, 2025-02-19, 2025-02-26, 2025-03-10, 2025-03-12, 2025-03-19, 2025-03-27, 2025-04-02, 2025-04-09, 2025-04-23, 2025-04-30, 2025-05-07, 2025-05-14, 2025-05-22, 2025-05-28, 2025-06-05, 2025-06-13, 2025-06-19, 2025-06-26, 2025-07-01, 2025-07-10, 2025-07-16, 2025-07-25, 2025-08-02, 2025-08-11, 2025-08-13, 2025-08-21, 2025-08-27, 2025-09-04, 2025-09-10, 2025-09-17, 2025-09-26, 2025-10-04, 2025-10-11, 2025-10-20, 2025-10-24, 2025-10-28, 2025-11-05, 2025-11-12, 2025-11-19, 2025-12-03, 2025-12-19, 2026-01-22, 2026-01-28, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27, 2026-03-06, 2026-03-11</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -4533,12 +4445,12 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2024-01-12, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-22, 2024-02-29, 2024-03-05, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-07, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-13, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-18, 2025-07-24, 2025-07-28, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-27, 2025-09-05, 2025-09-11, 2025-09-26, 2025-10-09, 2025-10-18, 2025-10-24, 2025-10-31, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-28, 2025-12-06, 2025-12-19, 2026-01-09, 2026-01-16, 2026-01-30, 2026-02-06, 2026-02-09, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-06, 2026-03-13</t>
+          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2024-01-26, 2024-01-30, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-23, 2024-03-01, 2024-03-08, 2024-03-15, 2024-03-22, 2024-04-05, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-07, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-29, 2024-12-06, 2024-12-13, 2025-01-10, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-23, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-10, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-28, 2025-09-05, 2025-09-12, 2025-09-26, 2025-10-11, 2025-10-18, 2025-10-24, 2025-10-31, 2025-11-06, 2025-11-21, 2025-11-28, 2025-12-06, 2025-12-19, 2026-01-09, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-06, 2026-03-14</t>
+          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -4623,12 +4535,12 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2025-10-01, 2025-10-15, 2025-10-29, 2025-11-12, 2025-11-19, 2025-12-03, 2026-01-07, 2026-01-21, 2026-02-04, 2026-02-11, 2026-02-23, 2026-03-02, 2026-03-09, 2026-03-18</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-23</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2025-10-01, 2025-10-29, 2025-11-12, 2025-11-14, 2025-12-03, 2026-01-21, 2026-02-04, 2026-02-11, 2026-02-23, 2026-03-09, 2026-03-18</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-23</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -4713,12 +4625,12 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2023-02-10, 2023-02-16, 2023-02-24, 2023-03-06, 2023-03-13, 2023-03-21, 2023-03-23, 2023-03-31, 2023-04-10, 2023-04-15, 2023-04-21, 2023-04-28, 2023-05-06, 2023-05-12, 2023-05-20, 2023-05-26, 2023-06-03, 2023-06-09, 2023-06-16, 2023-06-24, 2023-06-30, 2023-07-07, 2023-08-08, 2023-08-11, 2023-08-22, 2023-08-26, 2023-09-01, 2023-09-09, 2023-09-16, 2023-09-23, 2023-09-29, 2023-10-09, 2023-10-17, 2023-10-20, 2023-10-27, 2023-11-03, 2023-11-11, 2023-11-17, 2023-11-27, 2023-12-02, 2023-12-07, 2023-12-18, 2023-12-22, 2023-12-29, 2024-01-10, 2024-01-13, 2024-01-19, 2024-01-27, 2024-02-01, 2024-02-14, 2024-02-20, 2024-02-24, 2024-03-05, 2024-03-12, 2024-03-18, 2024-03-22, 2024-04-02, 2024-04-09, 2024-04-13, 2024-04-20, 2024-04-26, 2024-05-02, 2024-05-11, 2024-05-18, 2024-05-25, 2024-06-04, 2024-06-11, 2024-06-19, 2024-06-22, 2024-06-29, 2024-07-09, 2024-07-11, 2024-07-19, 2024-07-27, 2024-08-01, 2024-08-08, 2024-08-17, 2024-08-24, 2024-08-31, 2024-09-07, 2024-09-14, 2024-09-21, 2024-09-28, 2024-10-05, 2024-10-15, 2024-10-19, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-23, 2024-11-30, 2024-12-06, 2024-12-13, 2024-12-21, 2025-01-02, 2025-01-11, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-29, 2025-04-04, 2025-04-11, 2025-04-24, 2025-04-29, 2025-05-10, 2025-05-16, 2025-05-24, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-25, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-17, 2025-10-23, 2025-10-29, 2025-10-31, 2025-11-07, 2025-11-11, 2025-11-20, 2025-11-28, 2025-12-04, 2025-12-09, 2025-12-19, 2025-12-23, 2026-01-30, 2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28, 2026-03-07, 2026-03-14</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2023-02-13, 2023-02-16, 2023-02-24, 2023-02-27, 2023-03-06, 2023-03-13, 2023-03-22, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-17, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-15, 2023-05-23, 2023-05-29, 2023-06-03, 2023-06-05, 2023-06-13, 2023-06-20, 2023-06-26, 2023-07-04, 2023-07-13, 2023-08-09, 2023-08-14, 2023-08-24, 2023-08-28, 2023-09-04, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-02, 2023-10-10, 2023-10-19, 2023-10-24, 2023-10-31, 2023-11-08, 2023-11-16, 2023-11-20, 2023-11-28, 2023-12-05, 2023-12-11, 2023-12-19, 2023-12-26, 2024-01-02, 2024-01-10, 2024-01-16, 2024-01-24, 2024-01-30, 2024-02-06, 2024-02-14, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-12, 2024-03-19, 2024-03-26, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-26, 2024-04-30, 2024-05-07, 2024-05-18, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-22, 2024-06-25, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-10, 2024-08-17, 2024-08-24, 2024-08-31, 2024-09-07, 2024-09-14, 2024-09-21, 2024-09-28, 2024-10-05, 2024-10-15, 2024-10-19, 2024-10-25, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-07, 2024-12-14, 2024-12-21, 2025-01-02, 2025-01-11, 2025-01-17, 2025-01-25, 2025-01-31, 2025-02-07, 2025-02-15, 2025-02-21, 2025-02-28, 2025-03-09, 2025-03-14, 2025-03-21, 2025-03-29, 2025-04-05, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-10, 2025-05-16, 2025-05-24, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-28, 2025-07-05, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-02, 2025-08-08, 2025-08-16, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-20, 2025-09-27, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-29, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-29, 2025-12-06, 2025-12-12, 2025-12-20, 2026-01-23, 2026-01-30, 2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28, 2026-03-07, 2026-03-14</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -4803,12 +4715,12 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2023-08-01, 2023-08-28, 2023-10-03, 2023-11-29, 2024-01-25, 2024-01-31, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-20, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-04, 2024-10-10, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-20, 2024-12-27, 2025-01-03, 2025-01-10, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-23, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-10, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-28, 2025-12-05, 2025-12-12, 2026-01-16, 2026-01-19, 2026-01-20, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27, 2026-03-06, 2026-03-13</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2023-08-28, 2023-10-03, 2024-01-25, 2024-01-31, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-22, 2024-03-02, 2024-03-12, 2024-03-15, 2024-03-20, 2024-03-22, 2024-04-11, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-07, 2024-06-14, 2024-06-22, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-21, 2024-09-28, 2024-10-05, 2024-10-12, 2024-10-19, 2024-10-26, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-07, 2024-12-14, 2024-12-21, 2024-12-28, 2025-01-04, 2025-01-11, 2025-01-18, 2025-01-25, 2025-02-01, 2025-02-08, 2025-02-15, 2025-02-22, 2025-03-05, 2025-03-08, 2025-03-15, 2025-03-22, 2025-03-29, 2025-04-05, 2025-04-12, 2025-04-26, 2025-05-03, 2025-05-10, 2025-05-17, 2025-05-24, 2025-05-31, 2025-06-07, 2025-06-14, 2025-06-21, 2025-06-28, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-13, 2025-09-20, 2025-09-27, 2025-10-04, 2025-10-11, 2025-10-18, 2025-10-25, 2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29, 2025-12-06, 2025-12-13, 2026-01-17, 2026-01-20, 2026-01-24, 2026-01-31, 2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28, 2026-03-07, 2026-03-14</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -4893,12 +4805,12 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2023-07-31, 2023-08-29, 2023-10-11, 2023-11-30, 2024-04-25, 2024-05-23, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-11-02, 2024-11-08, 2024-11-25, 2024-11-29, 2024-12-07, 2024-12-14, 2024-12-20, 2025-01-19, 2025-01-25, 2025-02-01, 2025-02-08, 2025-02-15, 2025-02-22, 2025-02-28, 2025-03-08, 2025-03-15, 2025-03-20, 2025-03-29, 2025-04-07, 2025-04-12, 2025-04-26, 2025-05-03, 2025-05-09, 2025-05-17, 2025-05-22, 2025-05-30, 2025-06-02, 2025-06-12, 2025-06-21, 2025-06-28, 2025-07-03, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-08, 2025-08-14, 2025-08-23, 2025-08-28, 2025-09-06, 2025-09-11, 2025-09-19, 2025-09-30, 2025-10-04, 2025-10-11, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-27, 2025-11-29, 2025-12-13, 2026-01-15, 2026-01-16, 2026-01-23, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05, 2026-03-13, 2026-03-19</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2023-10-11, 2024-04-25, 2024-05-23, 2024-08-28, 2024-08-29, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-11, 2024-10-18, 2024-10-27, 2024-11-02, 2024-11-08, 2024-11-25, 2024-11-29, 2024-12-07, 2024-12-14, 2024-12-20, 2025-01-19, 2025-01-25, 2025-02-01, 2025-02-08, 2025-02-16, 2025-02-22, 2025-03-08, 2025-03-18, 2025-03-22, 2025-03-29, 2025-04-07, 2025-04-13, 2025-04-30, 2025-05-08, 2025-05-12, 2025-05-21, 2025-05-29, 2025-06-01, 2025-06-07, 2025-06-14, 2025-06-21, 2025-06-28, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-12, 2025-09-19, 2025-10-01, 2025-10-04, 2025-10-11, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-15, 2025-11-21, 2025-11-29, 2025-12-06, 2025-12-19, 2026-01-16, 2026-01-23, 2026-01-30, 2026-02-05, 2026-02-13, 2026-02-21, 2026-02-27, 2026-03-06, 2026-03-13</t>
+          <t>2026-02-05, 2026-02-13, 2026-02-21, 2026-02-27</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -4983,12 +4895,12 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2025-08-14, 2025-08-21, 2025-08-28, 2025-09-05, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-08, 2026-01-15, 2026-01-22, 2026-01-29, 2026-02-04, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05, 2026-03-12</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2025-08-15, 2025-08-22, 2025-09-02, 2025-09-05, 2025-09-13, 2025-09-19, 2025-09-26, 2025-10-04, 2025-10-11, 2025-10-23, 2025-10-28, 2025-10-31, 2025-11-11, 2025-11-14, 2025-11-21, 2025-12-04, 2025-12-09, 2025-12-12, 2025-12-19, 2026-01-09, 2026-01-19, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-28, 2026-03-07, 2026-03-13</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-28</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         <v>4</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
         <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         <v>4</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1236,10 +1236,10 @@
         <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="11">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1384,10 +1384,10 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="X12" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="13">
@@ -1446,10 +1446,10 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X13" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="14">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="X14" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="15">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1796,10 +1796,10 @@
         <v>4</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1898,10 +1898,10 @@
         <v>4</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1992,10 +1992,10 @@
         <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X19" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="20">
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2206,10 +2206,10 @@
         <v>3</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="X22" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="23">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
         <v>4</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26">
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2510,10 +2510,10 @@
         <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X26" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="27">
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2670,10 +2670,10 @@
         <v>3</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X28" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="29">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2826,10 +2826,10 @@
         <v>3</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X30" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="31">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P32" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
         <v>4</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -3146,10 +3146,10 @@
         <v>2</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="X34" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="35">
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -3244,10 +3244,10 @@
         <v>4</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         <v>4</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="38">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P39" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
         <v>4</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -3668,10 +3668,10 @@
         <v>4</v>
       </c>
       <c r="W40" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41">
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X41" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="42">
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P43" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
         <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X44" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="45">
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -4098,10 +4098,10 @@
         <v>4</v>
       </c>
       <c r="W45" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="46">
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -4196,10 +4196,10 @@
         <v>3</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="47">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -4290,10 +4290,10 @@
         <v>3</v>
       </c>
       <c r="W47" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="X47" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="48">
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4380,10 +4380,10 @@
         <v>4</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="49">
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4470,10 +4470,10 @@
         <v>3</v>
       </c>
       <c r="W49" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X49" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="50">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P50" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>2</v>
       </c>
       <c r="W50" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X50" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="51">
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -4650,10 +4650,10 @@
         <v>4</v>
       </c>
       <c r="W51" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="52">
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         <v>3</v>
       </c>
       <c r="W52" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="53">
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -4830,10 +4830,10 @@
         <v>3</v>
       </c>
       <c r="W53" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X53" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="54">
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -4920,10 +4920,10 @@
         <v>4</v>
       </c>
       <c r="W54" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="X54" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         <v>4</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
         <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         <v>4</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1236,10 +1236,10 @@
         <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1384,10 +1384,10 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="13">
@@ -1446,10 +1446,10 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X13" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="14">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="X14" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1796,10 +1796,10 @@
         <v>4</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1898,10 +1898,10 @@
         <v>4</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1992,10 +1992,10 @@
         <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X19" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2206,10 +2206,10 @@
         <v>3</v>
       </c>
       <c r="W22" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="23">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
         <v>4</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2510,10 +2510,10 @@
         <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X26" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="27">
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2670,10 +2670,10 @@
         <v>3</v>
       </c>
       <c r="W28" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="29">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2826,10 +2826,10 @@
         <v>3</v>
       </c>
       <c r="W30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="31">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
         <v>4</v>
       </c>
       <c r="W32" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -3146,10 +3146,10 @@
         <v>2</v>
       </c>
       <c r="W34" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35">
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -3244,10 +3244,10 @@
         <v>4</v>
       </c>
       <c r="W35" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         <v>4</v>
       </c>
       <c r="W37" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
         <v>4</v>
       </c>
       <c r="W39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P40" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -3668,10 +3668,10 @@
         <v>4</v>
       </c>
       <c r="W40" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P41" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         <v>2</v>
       </c>
       <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" t="n">
         <v>0.5</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="42">
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="P43" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
         <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X44" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="45">
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -4098,10 +4098,10 @@
         <v>4</v>
       </c>
       <c r="W45" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X45" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -4196,10 +4196,10 @@
         <v>3</v>
       </c>
       <c r="W46" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="47">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -4290,10 +4290,10 @@
         <v>3</v>
       </c>
       <c r="W47" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="X47" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="48">
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P48" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4380,10 +4380,10 @@
         <v>4</v>
       </c>
       <c r="W48" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X48" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4470,10 +4470,10 @@
         <v>3</v>
       </c>
       <c r="W49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="50">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>2</v>
       </c>
       <c r="W50" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X50" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="51">
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -4650,10 +4650,10 @@
         <v>4</v>
       </c>
       <c r="W51" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X51" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         <v>3</v>
       </c>
       <c r="W52" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X52" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="53">
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -4830,10 +4830,10 @@
         <v>3</v>
       </c>
       <c r="W53" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="54">
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P54" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -4920,10 +4920,10 @@
         <v>4</v>
       </c>
       <c r="W54" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="X54" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,7 +546,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PUERTA DORADA CRISTALINA</t>
+          <t>AMARETTO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -557,20 +557,16 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Germán Baquero</t>
+          <t>José Luis Suarez</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kelly Gutierrez</t>
+          <t>Abimael Padilla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PUERTA DORADA</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>JUEVES</t>
@@ -583,12 +579,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>02:00:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -598,7 +594,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -614,7 +610,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-06, 2026-03-20, 2026-03-30</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -624,20 +620,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-20</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="U2" t="n">
         <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -648,7 +644,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AMARETTO</t>
+          <t>RIVERBAY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -664,14 +660,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Abimael Padilla</t>
+          <t>Orlando Iguaran</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>MARTES</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -681,7 +677,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -691,12 +687,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -707,22 +703,22 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -746,7 +742,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RIVERBAY</t>
+          <t>C DEL PARQUE TAYRONA APTOS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -757,44 +753,40 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>José Luis Suarez</t>
+          <t>Germán Baquero</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orlando Iguaran</t>
+          <t>Carlos Sandoval</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CIUDAD DEL PARQUE</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
+          <t xml:space="preserve">JUEVES </t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>02:00:00</t>
-        </is>
-      </c>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -805,35 +797,35 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20</t>
         </is>
       </c>
       <c r="U4" t="n">
         <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5">
@@ -844,7 +836,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C DEL PARQUE TAYRONA APTOS</t>
+          <t>DIMARO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -855,40 +847,36 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Germán Baquero</t>
+          <t>José Luis Suarez</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Carlos Sandoval</t>
+          <t xml:space="preserve">Julio Curvelo </t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CIUDAD DEL PARQUE</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUEVES </t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -897,21 +885,37 @@
       <c r="P5" t="n">
         <v>4</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-10, 2026-03-11, 2026-03-18, 2026-03-31</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-11, 2026-03-20, 2026-03-31</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-11, 2026-03-18</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-11, 2026-03-20</t>
+        </is>
+      </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
@@ -922,7 +926,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DIMARO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -938,31 +942,31 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Julio Curvelo </t>
+          <t>Erich Camargo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>MIERCOLES</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -971,21 +975,37 @@
       <c r="P6" t="n">
         <v>4</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-14</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-14</t>
+        </is>
+      </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -996,7 +1016,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>PARKSIDE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1012,31 +1032,31 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Erich Camargo</t>
+          <t>Ivan Barbosa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>MARTES</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1045,21 +1065,37 @@
       <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09, 2026-03-18</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2026-03-09, 2026-03-18, 2026-03-21</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8">
@@ -1070,7 +1106,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PARKSIDE</t>
+          <t>PUERTA DORADA ARRECIFE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1081,36 +1117,36 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>José Luis Suarez</t>
+          <t>Germán Baquero</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ivan Barbosa</t>
+          <t>Tatiana Navarro</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>LUNES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1119,21 +1155,37 @@
       <c r="P8" t="n">
         <v>4</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1144,7 +1196,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PUERTA DORADA ARRECIFE</t>
+          <t>PUERTA DORADA MARISMA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1160,54 +1212,70 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tatiana Navarro</t>
+          <t>Carlos Quiroz</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>SABADO</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-24, 2026-03-28</t>
         </is>
       </c>
       <c r="O9" t="n">
         <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21</t>
+        </is>
+      </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="10">
@@ -1218,7 +1286,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PUERTA DORADA MARISMA</t>
+          <t>PUERTA DORADA NATURA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1234,54 +1302,70 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Carlos Quiroz</t>
+          <t>Lina Olarte</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SABADO</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-24, 2026-03-28</t>
-        </is>
-      </c>
       <c r="O10" t="n">
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-13, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-13, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+        </is>
+      </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
@@ -1292,7 +1376,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PUERTA DORADA NATURA</t>
+          <t>RIVERBLUE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1303,12 +1387,12 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Germán Baquero</t>
+          <t>José Luis Suarez</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lina Olarte</t>
+          <t>Jeeniffer Perez</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1341,21 +1425,37 @@
       <c r="P11" t="n">
         <v>4</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-27</t>
+        </is>
+      </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1366,7 +1466,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RIVERBLUE</t>
+          <t>PUERTA DORADA CRISTALINA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1377,28 +1477,40 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>José Luis Suarez</t>
+          <t>Germán Baquero</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeeniffer Perez</t>
+          <t>Kelly Gutierrez</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PUERTA DORADA</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
@@ -1415,21 +1527,127 @@
       <c r="P12" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-06, 2026-03-20, 2026-03-30</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-20</t>
+        </is>
+      </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LOTE SEVILLA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Germán Baquero</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Danny Gerez</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-24, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-24, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -622,17 +622,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -715,22 +715,22 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>2026-03-05, 2026-03-11, 2026-03-19, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-11, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-14, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-14, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -828,13 +828,13 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
         <v>3</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X4" t="n">
         <v>0.75</v>
@@ -899,35 +899,35 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-10, 2026-03-11, 2026-03-18, 2026-03-31</t>
+          <t>2026-03-06, 2026-03-10, 2026-03-11, 2026-03-20, 2026-03-31</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-20, 2026-03-31</t>
+          <t>2026-03-09, 2026-03-11, 2026-03-20, 2026-03-31</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-18</t>
+          <t>2026-03-06, 2026-03-11, 2026-03-20</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-20</t>
+          <t>2026-03-11, 2026-03-20</t>
         </is>
       </c>
       <c r="U5" t="n">
         <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
         <v>0.75</v>
       </c>
       <c r="X5" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -989,7 +989,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+          <t>2026-03-06, 2026-03-14</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+          <t>2026-03-06, 2026-03-14</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
         <v>2</v>
       </c>
       <c r="W6" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X6" t="n">
         <v>0.5</v>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-18</t>
+          <t>2026-03-09, 2026-03-18</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-18, 2026-03-21</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-18, 2026-03-21</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-21, 2026-03-30</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-21</t>
         </is>
       </c>
       <c r="U10" t="n">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-27</t>
+          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-27</t>
+          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
       <c r="U11" t="n">
@@ -1541,35 +1541,35 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-06, 2026-03-20, 2026-03-30</t>
+          <t>2026-03-03, 2026-03-11, 2026-03-20, 2026-03-30</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-20</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="13">

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,122 +429,122 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Gerente</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Director de obra</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ValidacionParametrización</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Cluster</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>HorarioIntermedia</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>HorarioSemanal</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ConteoIntermedia</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ConteoSemanal</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>RealIntermedia</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RealSemanal</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>CoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>CoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>CumplimientoIntermedia</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>CumplimientoSemanal</t>
         </is>
@@ -618,22 +630,18 @@
           <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
-        </is>
-      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
         <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -807,22 +815,22 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
+          <t>2026-03-06, 2026-03-20</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>2026-03-06, 2026-03-14, 2026-03-20</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-14, 2026-03-20</t>
-        </is>
-      </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
         <v>3</v>
       </c>
       <c r="W4" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X4" t="n">
         <v>0.75</v>
@@ -897,25 +905,25 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-03-11, 2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
@@ -987,22 +995,22 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>2026-03-06, 2026-03-14</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-14</t>
-        </is>
-      </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>2</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="X6" t="n">
         <v>0.5</v>
@@ -1165,24 +1173,20 @@
           <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
         <is>
           <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
-        </is>
-      </c>
       <c r="U8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -1262,20 +1266,20 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-14, 2026-03-21</t>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
       <c r="U9" t="n">
         <v>4</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
